--- a/Docs/人格牌.xlsx
+++ b/Docs/人格牌.xlsx
@@ -5,35 +5,45 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29347\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\确定版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731A398E-B762-4398-9CBB-86506821CB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC728E53-8E5A-4F92-915F-1FBDD6A0FCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="848" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="定义表" sheetId="8" r:id="rId1"/>
-    <sheet name="全局配置" sheetId="4" r:id="rId2"/>
-    <sheet name="关卡流程" sheetId="5" r:id="rId3"/>
-    <sheet name="牌型配置" sheetId="1" r:id="rId4"/>
+    <sheet name="全局配置" sheetId="4" r:id="rId1"/>
+    <sheet name="关卡流程" sheetId="5" r:id="rId2"/>
+    <sheet name="牌型配置" sheetId="1" r:id="rId3"/>
+    <sheet name="卡牌配置" sheetId="7" r:id="rId4"/>
     <sheet name="人格牌配置" sheetId="6" r:id="rId5"/>
-    <sheet name="人格牌概率" sheetId="9" r:id="rId6"/>
-    <sheet name="手牌配置" sheetId="7" r:id="rId7"/>
+    <sheet name="人格牌概率配置" sheetId="9" r:id="rId6"/>
+    <sheet name="人格牌品质配置" sheetId="10" r:id="rId7"/>
     <sheet name="图片配置" sheetId="2" r:id="rId8"/>
     <sheet name="文本配置" sheetId="3" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="510">
   <si>
     <t>牌型名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -144,18 +154,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>人格牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>卡牌名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>card_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CARD_053</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -188,232 +190,6 @@
     <t>CARD_062</t>
   </si>
   <si>
-    <t>card_002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>card_003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>card_004</t>
-  </si>
-  <si>
-    <t>card_005</t>
-  </si>
-  <si>
-    <t>card_006</t>
-  </si>
-  <si>
-    <t>card_007</t>
-  </si>
-  <si>
-    <t>card_008</t>
-  </si>
-  <si>
-    <t>card_009</t>
-  </si>
-  <si>
-    <t>card_010</t>
-  </si>
-  <si>
-    <t>card_011</t>
-  </si>
-  <si>
-    <t>card_012</t>
-  </si>
-  <si>
-    <t>card_013</t>
-  </si>
-  <si>
-    <t>card_014</t>
-  </si>
-  <si>
-    <t>card_015</t>
-  </si>
-  <si>
-    <t>card_016</t>
-  </si>
-  <si>
-    <t>card_017</t>
-  </si>
-  <si>
-    <t>card_018</t>
-  </si>
-  <si>
-    <t>card_019</t>
-  </si>
-  <si>
-    <t>card_020</t>
-  </si>
-  <si>
-    <t>card_021</t>
-  </si>
-  <si>
-    <t>card_022</t>
-  </si>
-  <si>
-    <t>card_023</t>
-  </si>
-  <si>
-    <t>card_024</t>
-  </si>
-  <si>
-    <t>card_025</t>
-  </si>
-  <si>
-    <t>card_026</t>
-  </si>
-  <si>
-    <t>card_027</t>
-  </si>
-  <si>
-    <t>card_028</t>
-  </si>
-  <si>
-    <t>card_029</t>
-  </si>
-  <si>
-    <t>card_030</t>
-  </si>
-  <si>
-    <t>card_031</t>
-  </si>
-  <si>
-    <t>card_032</t>
-  </si>
-  <si>
-    <t>card_033</t>
-  </si>
-  <si>
-    <t>card_034</t>
-  </si>
-  <si>
-    <t>card_035</t>
-  </si>
-  <si>
-    <t>card_036</t>
-  </si>
-  <si>
-    <t>card_037</t>
-  </si>
-  <si>
-    <t>card_038</t>
-  </si>
-  <si>
-    <t>card_039</t>
-  </si>
-  <si>
-    <t>card_040</t>
-  </si>
-  <si>
-    <t>card_041</t>
-  </si>
-  <si>
-    <t>card_042</t>
-  </si>
-  <si>
-    <t>card_043</t>
-  </si>
-  <si>
-    <t>card_044</t>
-  </si>
-  <si>
-    <t>card_045</t>
-  </si>
-  <si>
-    <t>card_046</t>
-  </si>
-  <si>
-    <t>card_047</t>
-  </si>
-  <si>
-    <t>card_048</t>
-  </si>
-  <si>
-    <t>card_049</t>
-  </si>
-  <si>
-    <t>card_050</t>
-  </si>
-  <si>
-    <t>card_051</t>
-  </si>
-  <si>
-    <t>card_052</t>
-  </si>
-  <si>
-    <t>card_053</t>
-  </si>
-  <si>
-    <t>card_054</t>
-  </si>
-  <si>
-    <t>card_055</t>
-  </si>
-  <si>
-    <t>card_056</t>
-  </si>
-  <si>
-    <t>card_057</t>
-  </si>
-  <si>
-    <t>card_058</t>
-  </si>
-  <si>
-    <t>card_059</t>
-  </si>
-  <si>
-    <t>card_060</t>
-  </si>
-  <si>
-    <t>card_061</t>
-  </si>
-  <si>
-    <t>card_062</t>
-  </si>
-  <si>
-    <t>card_063</t>
-  </si>
-  <si>
-    <t>rule_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rule_002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rule_003</t>
-  </si>
-  <si>
-    <t>rule_004</t>
-  </si>
-  <si>
-    <t>rule_005</t>
-  </si>
-  <si>
-    <t>rule_006</t>
-  </si>
-  <si>
-    <t>rule_007</t>
-  </si>
-  <si>
-    <t>rule_008</t>
-  </si>
-  <si>
-    <t>rule_009</t>
-  </si>
-  <si>
-    <t>rule_010</t>
-  </si>
-  <si>
-    <t>rule_011</t>
-  </si>
-  <si>
-    <t>rule_012</t>
-  </si>
-  <si>
     <t>每关基础出牌次数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -482,664 +258,1460 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>阶段_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手牌_id</t>
+    <t>STAGE_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAGE_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAGE_03</t>
+  </si>
+  <si>
+    <t>STAGE_04</t>
+  </si>
+  <si>
+    <t>STAGE_05</t>
+  </si>
+  <si>
+    <t>STAGE_06</t>
+  </si>
+  <si>
+    <t>STAGE_07</t>
+  </si>
+  <si>
+    <t>STAGE_08</t>
+  </si>
+  <si>
+    <t>STAGE_09</t>
+  </si>
+  <si>
+    <t>STAGE_10</t>
+  </si>
+  <si>
+    <t>STAGE_11</t>
+  </si>
+  <si>
+    <t>STAGE_12</t>
+  </si>
+  <si>
+    <t>STAGE_13</t>
+  </si>
+  <si>
+    <t>关卡名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手牌限制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弃牌限制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人格牌生成数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分数类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分数参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人格牌生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关分数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人格牌名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励类型1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励参数2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励类型2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励参数1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进阶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件阈值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附加条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果类型1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果参数1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果参数2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>独立结算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T01</t>
+  </si>
+  <si>
+    <t>T02</t>
+  </si>
+  <si>
+    <t>T03</t>
+  </si>
+  <si>
+    <t>T04</t>
+  </si>
+  <si>
+    <t>T05</t>
+  </si>
+  <si>
+    <t>T06</t>
+  </si>
+  <si>
+    <t>T07</t>
+  </si>
+  <si>
+    <t>T08</t>
+  </si>
+  <si>
+    <t>T09</t>
+  </si>
+  <si>
+    <t>与上一手牌型相同</t>
+  </si>
+  <si>
+    <t>等于</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>增加筹码</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>计分牌数量</t>
+  </si>
+  <si>
+    <t>大于等于</t>
+  </si>
+  <si>
+    <t>增加倍率</t>
+  </si>
+  <si>
+    <t>已使用弃牌次数</t>
+  </si>
+  <si>
+    <t>增加筹码和倍率</t>
+  </si>
+  <si>
+    <t>命中AI偏好</t>
+  </si>
+  <si>
+    <t>剩余弃牌次数</t>
+  </si>
+  <si>
+    <t>每单位增加倍率</t>
+  </si>
+  <si>
+    <t>本局移除牌数量</t>
+  </si>
+  <si>
+    <t>本局新增牌数量</t>
+  </si>
+  <si>
+    <t>每单位增加筹码</t>
+  </si>
+  <si>
+    <t>稀有</t>
+  </si>
+  <si>
+    <t>连续使用相同牌型次数</t>
+  </si>
+  <si>
+    <t>最终倍率乘算</t>
+  </si>
+  <si>
+    <t>牌库数量</t>
+  </si>
+  <si>
+    <t>小于</t>
+  </si>
+  <si>
+    <t>其他人格触发次数</t>
+  </si>
+  <si>
+    <t>特殊</t>
+  </si>
+  <si>
+    <t>小于等于</t>
+  </si>
+  <si>
+    <t>另有计分牌数量条件*</t>
+  </si>
+  <si>
+    <t>剩余出牌次数</t>
+  </si>
+  <si>
+    <t>剩余弃牌次数=0</t>
+  </si>
+  <si>
+    <t>人格触发次数</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t>T12</t>
+  </si>
+  <si>
+    <t>T13</t>
+  </si>
+  <si>
+    <t>T14</t>
+  </si>
+  <si>
+    <t>T15</t>
+  </si>
+  <si>
+    <t>T16</t>
+  </si>
+  <si>
+    <t>白色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111111（暂定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111112（暂定</t>
+  </si>
+  <si>
+    <t>111113（暂定</t>
+  </si>
+  <si>
+    <t>111114（暂定</t>
+  </si>
+  <si>
+    <t>111115（暂定</t>
+  </si>
+  <si>
+    <t>111116（暂定</t>
+  </si>
+  <si>
+    <t>111117（暂定</t>
+  </si>
+  <si>
+    <t>111118（暂定</t>
+  </si>
+  <si>
+    <t>111119（暂定</t>
+  </si>
+  <si>
+    <t>111120（暂定</t>
+  </si>
+  <si>
+    <t>111121（暂定</t>
+  </si>
+  <si>
+    <t>111122（暂定</t>
+  </si>
+  <si>
+    <t>111123（暂定</t>
+  </si>
+  <si>
+    <t>111124（暂定</t>
+  </si>
+  <si>
+    <t>111125（暂定</t>
+  </si>
+  <si>
+    <t>111126（暂定</t>
+  </si>
+  <si>
+    <t>黑桃A</t>
+  </si>
+  <si>
+    <t>黑桃2</t>
+  </si>
+  <si>
+    <t>黑桃3</t>
+  </si>
+  <si>
+    <t>黑桃4</t>
+  </si>
+  <si>
+    <t>黑桃5</t>
+  </si>
+  <si>
+    <t>黑桃6</t>
+  </si>
+  <si>
+    <t>黑桃7</t>
+  </si>
+  <si>
+    <t>黑桃8</t>
+  </si>
+  <si>
+    <t>黑桃9</t>
+  </si>
+  <si>
+    <t>黑桃10</t>
+  </si>
+  <si>
+    <t>黑桃J</t>
+  </si>
+  <si>
+    <t>黑桃Q</t>
+  </si>
+  <si>
+    <t>黑桃K</t>
+  </si>
+  <si>
+    <t>红桃A</t>
+  </si>
+  <si>
+    <t>红桃2</t>
+  </si>
+  <si>
+    <t>红桃3</t>
+  </si>
+  <si>
+    <t>红桃4</t>
+  </si>
+  <si>
+    <t>红桃5</t>
+  </si>
+  <si>
+    <t>红桃6</t>
+  </si>
+  <si>
+    <t>红桃7</t>
+  </si>
+  <si>
+    <t>红桃8</t>
+  </si>
+  <si>
+    <t>红桃9</t>
+  </si>
+  <si>
+    <t>红桃10</t>
+  </si>
+  <si>
+    <t>红桃J</t>
+  </si>
+  <si>
+    <t>红桃Q</t>
+  </si>
+  <si>
+    <t>红桃K</t>
+  </si>
+  <si>
+    <t>梅花A</t>
+  </si>
+  <si>
+    <t>梅花2</t>
+  </si>
+  <si>
+    <t>梅花3</t>
+  </si>
+  <si>
+    <t>梅花4</t>
+  </si>
+  <si>
+    <t>梅花5</t>
+  </si>
+  <si>
+    <t>梅花6</t>
+  </si>
+  <si>
+    <t>梅花7</t>
+  </si>
+  <si>
+    <t>梅花8</t>
+  </si>
+  <si>
+    <t>梅花9</t>
+  </si>
+  <si>
+    <t>梅花10</t>
+  </si>
+  <si>
+    <t>梅花J</t>
+  </si>
+  <si>
+    <t>梅花Q</t>
+  </si>
+  <si>
+    <t>梅花K</t>
+  </si>
+  <si>
+    <t>方块A</t>
+  </si>
+  <si>
+    <t>方块2</t>
+  </si>
+  <si>
+    <t>方块3</t>
+  </si>
+  <si>
+    <t>方块4</t>
+  </si>
+  <si>
+    <t>方块5</t>
+  </si>
+  <si>
+    <t>方块6</t>
+  </si>
+  <si>
+    <t>方块7</t>
+  </si>
+  <si>
+    <t>方块8</t>
+  </si>
+  <si>
+    <t>方块9</t>
+  </si>
+  <si>
+    <t>方块10</t>
+  </si>
+  <si>
+    <t>方块J</t>
+  </si>
+  <si>
+    <t>方块Q</t>
+  </si>
+  <si>
+    <t>方块K</t>
+  </si>
+  <si>
+    <t>卡牌名称</t>
+  </si>
+  <si>
+    <t>花色</t>
+  </si>
+  <si>
+    <t>点数</t>
+  </si>
+  <si>
+    <t>手牌</t>
+  </si>
+  <si>
+    <t>黑桃</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>红桃</t>
+  </si>
+  <si>
+    <t>梅花</t>
+  </si>
+  <si>
+    <t>方块</t>
+  </si>
+  <si>
+    <t>RULE_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RULE_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RULE_003</t>
+  </si>
+  <si>
+    <t>RULE_004</t>
+  </si>
+  <si>
+    <t>RULE_005</t>
+  </si>
+  <si>
+    <t>RULE_006</t>
+  </si>
+  <si>
+    <t>RULE_007</t>
+  </si>
+  <si>
+    <t>RULE_008</t>
+  </si>
+  <si>
+    <t>RULE_009</t>
+  </si>
+  <si>
+    <t>RULE_010</t>
+  </si>
+  <si>
+    <t>RULE_011</t>
+  </si>
+  <si>
+    <t>RULE_012</t>
+  </si>
+  <si>
+    <t>CARD_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CARD_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CARD_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CARD_004</t>
+  </si>
+  <si>
+    <t>CARD_005</t>
+  </si>
+  <si>
+    <t>CARD_006</t>
+  </si>
+  <si>
+    <t>CARD_007</t>
+  </si>
+  <si>
+    <t>CARD_008</t>
+  </si>
+  <si>
+    <t>CARD_009</t>
+  </si>
+  <si>
+    <t>CARD_010</t>
+  </si>
+  <si>
+    <t>CARD_011</t>
+  </si>
+  <si>
+    <t>CARD_012</t>
+  </si>
+  <si>
+    <t>CARD_013</t>
+  </si>
+  <si>
+    <t>CARD_014</t>
+  </si>
+  <si>
+    <t>CARD_015</t>
+  </si>
+  <si>
+    <t>CARD_016</t>
+  </si>
+  <si>
+    <t>CARD_017</t>
+  </si>
+  <si>
+    <t>CARD_018</t>
+  </si>
+  <si>
+    <t>CARD_019</t>
+  </si>
+  <si>
+    <t>CARD_020</t>
+  </si>
+  <si>
+    <t>CARD_021</t>
+  </si>
+  <si>
+    <t>CARD_022</t>
+  </si>
+  <si>
+    <t>CARD_023</t>
+  </si>
+  <si>
+    <t>CARD_024</t>
+  </si>
+  <si>
+    <t>CARD_025</t>
+  </si>
+  <si>
+    <t>CARD_026</t>
+  </si>
+  <si>
+    <t>CARD_027</t>
+  </si>
+  <si>
+    <t>CARD_028</t>
+  </si>
+  <si>
+    <t>CARD_029</t>
+  </si>
+  <si>
+    <t>CARD_030</t>
+  </si>
+  <si>
+    <t>CARD_031</t>
+  </si>
+  <si>
+    <t>CARD_032</t>
+  </si>
+  <si>
+    <t>CARD_033</t>
+  </si>
+  <si>
+    <t>CARD_034</t>
+  </si>
+  <si>
+    <t>CARD_035</t>
+  </si>
+  <si>
+    <t>CARD_036</t>
+  </si>
+  <si>
+    <t>CARD_037</t>
+  </si>
+  <si>
+    <t>CARD_038</t>
+  </si>
+  <si>
+    <t>CARD_039</t>
+  </si>
+  <si>
+    <t>CARD_040</t>
+  </si>
+  <si>
+    <t>CARD_041</t>
+  </si>
+  <si>
+    <t>CARD_042</t>
+  </si>
+  <si>
+    <t>CARD_043</t>
+  </si>
+  <si>
+    <t>CARD_044</t>
+  </si>
+  <si>
+    <t>CARD_045</t>
+  </si>
+  <si>
+    <t>CARD_046</t>
+  </si>
+  <si>
+    <t>CARD_047</t>
+  </si>
+  <si>
+    <t>CARD_048</t>
+  </si>
+  <si>
+    <t>CARD_049</t>
+  </si>
+  <si>
+    <t>CARD_050</t>
+  </si>
+  <si>
+    <t>CARD_051</t>
+  </si>
+  <si>
+    <t>CARD_052</t>
+  </si>
+  <si>
+    <t>参数1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>筹码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质名称</t>
+  </si>
+  <si>
+    <t>AI1出现概率</t>
+  </si>
+  <si>
+    <t>AI2出现概率</t>
+  </si>
+  <si>
+    <t>AI3出现概率</t>
+  </si>
+  <si>
+    <t>基础</t>
+  </si>
+  <si>
+    <t>进阶</t>
+  </si>
+  <si>
+    <t>异质</t>
+  </si>
+  <si>
+    <t>QUALITY_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QUALITY_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QUALITY_03</t>
+  </si>
+  <si>
+    <t>QUALITY_04</t>
+  </si>
+  <si>
+    <t>行为标签名称</t>
+  </si>
+  <si>
+    <t>基础品质阈值</t>
+  </si>
+  <si>
+    <t>进阶品质阈值</t>
+  </si>
+  <si>
+    <t>稀有品质阈值</t>
+  </si>
+  <si>
+    <t>异质品质阈值</t>
+  </si>
+  <si>
+    <t>AI1是否启用</t>
+  </si>
+  <si>
+    <t>AI2是否启用</t>
+  </si>
+  <si>
+    <t>AI3是否启用</t>
+  </si>
+  <si>
+    <t>同族重复惩罚</t>
+  </si>
+  <si>
+    <t>惯性/重复</t>
+  </si>
+  <si>
+    <t>投入/满载</t>
+  </si>
+  <si>
+    <t>克制/保留</t>
+  </si>
+  <si>
+    <t>偏好/专一</t>
+  </si>
+  <si>
+    <t>剥离/压缩</t>
+  </si>
+  <si>
+    <t>广纳/扩张</t>
+  </si>
+  <si>
+    <t>共振/联动</t>
+  </si>
+  <si>
+    <t>临界/绝境</t>
+  </si>
+  <si>
+    <t>背景底图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>准备界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>报告界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仓库界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人格牌原画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置界面_画面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置界面_声音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置界面_操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗界面_牌堆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗界面_卡牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss原画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡3</t>
+  </si>
+  <si>
+    <t>关卡4</t>
+  </si>
+  <si>
+    <t>关卡5</t>
+  </si>
+  <si>
+    <t>关卡6</t>
+  </si>
+  <si>
+    <t>关卡7</t>
+  </si>
+  <si>
+    <t>关卡8</t>
+  </si>
+  <si>
+    <t>关卡9</t>
+  </si>
+  <si>
+    <t>关卡10</t>
+  </si>
+  <si>
+    <t>商店界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店界面_金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人格牌01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人格牌02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人格牌03</t>
+  </si>
+  <si>
+    <t>人格牌04</t>
+  </si>
+  <si>
+    <t>人格牌05</t>
+  </si>
+  <si>
+    <t>人格牌06</t>
+  </si>
+  <si>
+    <t>人格牌07</t>
+  </si>
+  <si>
+    <t>人格牌08</t>
+  </si>
+  <si>
+    <t>人格牌09</t>
+  </si>
+  <si>
+    <t>人格牌10</t>
+  </si>
+  <si>
+    <t>人格牌11</t>
+  </si>
+  <si>
+    <t>人格牌12</t>
+  </si>
+  <si>
+    <t>人格牌13</t>
+  </si>
+  <si>
+    <t>人格牌14</t>
+  </si>
+  <si>
+    <t>人格牌15</t>
+  </si>
+  <si>
+    <t>人格牌16</t>
+  </si>
+  <si>
+    <t>牌库数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMAGE_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMAGE_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMAGE_003</t>
+  </si>
+  <si>
+    <t>IMAGE_004</t>
+  </si>
+  <si>
+    <t>IMAGE_005</t>
+  </si>
+  <si>
+    <t>IMAGE_006</t>
+  </si>
+  <si>
+    <t>IMAGE_007</t>
+  </si>
+  <si>
+    <t>IMAGE_008</t>
+  </si>
+  <si>
+    <t>IMAGE_009</t>
+  </si>
+  <si>
+    <t>IMAGE_010</t>
+  </si>
+  <si>
+    <t>IMAGE_011</t>
+  </si>
+  <si>
+    <t>IMAGE_012</t>
+  </si>
+  <si>
+    <t>IMAGE_013</t>
+  </si>
+  <si>
+    <t>IMAGE_014</t>
+  </si>
+  <si>
+    <t>IMAGE_015</t>
+  </si>
+  <si>
+    <t>IMAGE_016</t>
+  </si>
+  <si>
+    <t>IMAGE_017</t>
+  </si>
+  <si>
+    <t>IMAGE_018</t>
+  </si>
+  <si>
+    <t>IMAGE_019</t>
+  </si>
+  <si>
+    <t>IMAGE_020</t>
+  </si>
+  <si>
+    <t>IMAGE_021</t>
+  </si>
+  <si>
+    <t>IMAGE_022</t>
+  </si>
+  <si>
+    <t>IMAGE_023</t>
+  </si>
+  <si>
+    <t>IMAGE_024</t>
+  </si>
+  <si>
+    <t>IMAGE_025</t>
+  </si>
+  <si>
+    <t>IMAGE_026</t>
+  </si>
+  <si>
+    <t>IMAGE_027</t>
+  </si>
+  <si>
+    <t>IMAGE_028</t>
+  </si>
+  <si>
+    <t>IMAGE_029</t>
+  </si>
+  <si>
+    <t>IMAGE_030</t>
+  </si>
+  <si>
+    <t>IMAGE_031</t>
+  </si>
+  <si>
+    <t>IMAGE_032</t>
+  </si>
+  <si>
+    <t>IMAGE_033</t>
+  </si>
+  <si>
+    <t>IMAGE_034</t>
+  </si>
+  <si>
+    <t>IMAGE_035</t>
+  </si>
+  <si>
+    <t>IMAGE_036</t>
+  </si>
+  <si>
+    <t>IMAGE_037</t>
+  </si>
+  <si>
+    <t>IMAGE_038</t>
+  </si>
+  <si>
+    <t>IMAGE_039</t>
+  </si>
+  <si>
+    <t>IMAGE_040</t>
+  </si>
+  <si>
+    <t>IMAGE_041</t>
+  </si>
+  <si>
+    <t>IMAGE_042</t>
+  </si>
+  <si>
+    <t>IMAGE_043</t>
+  </si>
+  <si>
+    <t>IMAGE_044</t>
+  </si>
+  <si>
+    <t>IMAGE_045</t>
+  </si>
+  <si>
+    <t>IMAGE_046</t>
+  </si>
+  <si>
+    <t>IMAGE_047</t>
+  </si>
+  <si>
+    <t>IMAGE_048</t>
+  </si>
+  <si>
+    <t>IMAGE_049</t>
+  </si>
+  <si>
+    <t>IMAGE_050</t>
+  </si>
+  <si>
+    <t>IMAGE_051</t>
+  </si>
+  <si>
+    <t>IMAGE_052</t>
+  </si>
+  <si>
+    <t>IMAGE_053</t>
+  </si>
+  <si>
+    <t>IMAGE_054</t>
+  </si>
+  <si>
+    <t>IMAGE_055</t>
+  </si>
+  <si>
+    <t>IMAGE_056</t>
+  </si>
+  <si>
+    <t>IMAGE_057</t>
+  </si>
+  <si>
+    <t>IMAGE_058</t>
+  </si>
+  <si>
+    <t>IMAGE_059</t>
+  </si>
+  <si>
+    <t>IMAGE_060</t>
+  </si>
+  <si>
+    <t>IMAGE_061</t>
+  </si>
+  <si>
+    <t>IMAGE_062</t>
+  </si>
+  <si>
+    <t>IMAGE_063</t>
+  </si>
+  <si>
+    <t>IMAGE_064</t>
+  </si>
+  <si>
+    <t>IMAGE_065</t>
+  </si>
+  <si>
+    <t>IMAGE_066</t>
+  </si>
+  <si>
+    <t>IMAGE_067</t>
+  </si>
+  <si>
+    <t>IMAGE_068</t>
+  </si>
+  <si>
+    <t>IMAGE_069</t>
+  </si>
+  <si>
+    <t>IMAGE_070</t>
+  </si>
+  <si>
+    <t>IMAGE_071</t>
+  </si>
+  <si>
+    <t>IMAGE_072</t>
+  </si>
+  <si>
+    <t>IMAGE_073</t>
+  </si>
+  <si>
+    <t>IMAGE_074</t>
+  </si>
+  <si>
+    <t>IMAGE_075</t>
+  </si>
+  <si>
+    <t>IMAGE_076</t>
+  </si>
+  <si>
+    <t>IMAGE_077</t>
+  </si>
+  <si>
+    <t>IMAGE_078</t>
+  </si>
+  <si>
+    <t>IMAGE_079</t>
+  </si>
+  <si>
+    <t>IMAGE_080</t>
+  </si>
+  <si>
+    <t>IMAGE_081</t>
+  </si>
+  <si>
+    <t>IMAGE_082</t>
+  </si>
+  <si>
+    <t>IMAGE_083</t>
+  </si>
+  <si>
+    <t>IMAGE_084</t>
+  </si>
+  <si>
+    <t>IMAGE_085</t>
+  </si>
+  <si>
+    <t>IMAGE_086</t>
+  </si>
+  <si>
+    <t>IMAGE_087</t>
+  </si>
+  <si>
+    <t>IMAGE_088</t>
+  </si>
+  <si>
+    <t>IMAGE_089</t>
+  </si>
+  <si>
+    <t>IMAGE_090</t>
+  </si>
+  <si>
+    <t>IMAGE_091</t>
+  </si>
+  <si>
+    <t>IMAGE_092</t>
+  </si>
+  <si>
+    <t>IMAGE_093</t>
+  </si>
+  <si>
+    <t>IMAGE_094</t>
+  </si>
+  <si>
+    <t>IMAGE_095</t>
+  </si>
+  <si>
+    <t>IMAGE_096</t>
+  </si>
+  <si>
+    <t>IMAGE_097</t>
+  </si>
+  <si>
+    <t>IMAGE_098</t>
+  </si>
+  <si>
+    <t>IMAGE_099</t>
+  </si>
+  <si>
+    <t>IMAGE_100</t>
+  </si>
+  <si>
+    <t>IMAGE_101</t>
+  </si>
+  <si>
+    <t>IMAGE_102</t>
+  </si>
+  <si>
+    <t>绑定ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牌型ICON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PER_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PER_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PER_003</t>
+  </si>
+  <si>
+    <t>PER_004</t>
+  </si>
+  <si>
+    <t>PER_005</t>
+  </si>
+  <si>
+    <t>PER_006</t>
+  </si>
+  <si>
+    <t>PER_007</t>
+  </si>
+  <si>
+    <t>PER_008</t>
+  </si>
+  <si>
+    <t>PER_009</t>
+  </si>
+  <si>
+    <t>PER_010</t>
+  </si>
+  <si>
+    <t>PER_011</t>
+  </si>
+  <si>
+    <t>PER_012</t>
+  </si>
+  <si>
+    <t>PER_013</t>
+  </si>
+  <si>
+    <t>PER_014</t>
+  </si>
+  <si>
+    <t>PER_015</t>
+  </si>
+  <si>
+    <t>PER_016</t>
+  </si>
+  <si>
+    <t>品质_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规则_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手牌_ID</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>规则_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STAGE_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STAGE_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STAGE_03</t>
-  </si>
-  <si>
-    <t>STAGE_04</t>
-  </si>
-  <si>
-    <t>STAGE_05</t>
-  </si>
-  <si>
-    <t>STAGE_06</t>
-  </si>
-  <si>
-    <t>STAGE_07</t>
-  </si>
-  <si>
-    <t>STAGE_08</t>
-  </si>
-  <si>
-    <t>STAGE_09</t>
-  </si>
-  <si>
-    <t>STAGE_10</t>
-  </si>
-  <si>
-    <t>STAGE_11</t>
-  </si>
-  <si>
-    <t>STAGE_12</t>
-  </si>
-  <si>
-    <t>STAGE_13</t>
-  </si>
-  <si>
-    <t>关卡名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>顺序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手牌限制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弃牌限制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人格牌生成数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI生成3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI生成2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI生成1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分数类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分数参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人格牌生成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通关分数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人格牌_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>牌型图</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>card_064</t>
-  </si>
-  <si>
-    <t>card_065</t>
-  </si>
-  <si>
-    <t>card_066</t>
-  </si>
-  <si>
-    <t>card_067</t>
-  </si>
-  <si>
-    <t>card_068</t>
-  </si>
-  <si>
-    <t>card_069</t>
-  </si>
-  <si>
-    <t>card_070</t>
-  </si>
-  <si>
-    <t>card_071</t>
-  </si>
-  <si>
-    <t>card_072</t>
-  </si>
-  <si>
-    <t>card_073</t>
-  </si>
-  <si>
-    <t>card_074</t>
-  </si>
-  <si>
-    <t>card_075</t>
-  </si>
-  <si>
-    <t>card_076</t>
-  </si>
-  <si>
-    <t>card_077</t>
-  </si>
-  <si>
-    <t>card_078</t>
-  </si>
-  <si>
-    <t>card_079</t>
-  </si>
-  <si>
-    <t>card_080</t>
-  </si>
-  <si>
-    <t>人格牌名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>品质类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奖励类型1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奖励参数2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奖励类型2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奖励参数1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进阶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行为标签_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比较符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>条件阈值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>附加条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果类型1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果参数1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果参数2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>独立结算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>品质参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对应id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T01</t>
-  </si>
-  <si>
-    <t>T02</t>
-  </si>
-  <si>
-    <t>T03</t>
-  </si>
-  <si>
-    <t>T04</t>
-  </si>
-  <si>
-    <t>T05</t>
-  </si>
-  <si>
-    <t>T06</t>
-  </si>
-  <si>
-    <t>T07</t>
-  </si>
-  <si>
-    <t>T08</t>
-  </si>
-  <si>
-    <t>T09</t>
-  </si>
-  <si>
-    <t>与上一手牌型相同</t>
-  </si>
-  <si>
-    <t>等于</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>增加筹码</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>计分牌数量</t>
-  </si>
-  <si>
-    <t>大于等于</t>
-  </si>
-  <si>
-    <t>增加倍率</t>
-  </si>
-  <si>
-    <t>已使用弃牌次数</t>
-  </si>
-  <si>
-    <t>增加筹码和倍率</t>
-  </si>
-  <si>
-    <t>命中AI偏好</t>
-  </si>
-  <si>
-    <t>剩余弃牌次数</t>
-  </si>
-  <si>
-    <t>每单位增加倍率</t>
-  </si>
-  <si>
-    <t>本局移除牌数量</t>
-  </si>
-  <si>
-    <t>本局新增牌数量</t>
-  </si>
-  <si>
-    <t>每单位增加筹码</t>
-  </si>
-  <si>
-    <t>稀有</t>
-  </si>
-  <si>
-    <t>连续使用相同牌型次数</t>
-  </si>
-  <si>
-    <t>最终倍率乘算</t>
-  </si>
-  <si>
-    <t>牌库数量</t>
-  </si>
-  <si>
-    <t>小于</t>
-  </si>
-  <si>
-    <t>其他人格触发次数</t>
-  </si>
-  <si>
-    <t>特殊</t>
-  </si>
-  <si>
-    <t>小于等于</t>
-  </si>
-  <si>
-    <t>另有计分牌数量条件*</t>
-  </si>
-  <si>
-    <t>剩余出牌次数</t>
-  </si>
-  <si>
-    <t>剩余弃牌次数=0</t>
-  </si>
-  <si>
-    <t>人格触发次数</t>
-  </si>
-  <si>
-    <t>T10</t>
-  </si>
-  <si>
-    <t>T11</t>
-  </si>
-  <si>
-    <t>T12</t>
-  </si>
-  <si>
-    <t>T13</t>
-  </si>
-  <si>
-    <t>T14</t>
-  </si>
-  <si>
-    <t>T15</t>
-  </si>
-  <si>
-    <t>T16</t>
-  </si>
-  <si>
-    <t>刷新节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绿色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>111111（暂定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>111112（暂定</t>
-  </si>
-  <si>
-    <t>111113（暂定</t>
-  </si>
-  <si>
-    <t>111114（暂定</t>
-  </si>
-  <si>
-    <t>111115（暂定</t>
-  </si>
-  <si>
-    <t>111116（暂定</t>
-  </si>
-  <si>
-    <t>111117（暂定</t>
-  </si>
-  <si>
-    <t>111118（暂定</t>
-  </si>
-  <si>
-    <t>111119（暂定</t>
-  </si>
-  <si>
-    <t>111120（暂定</t>
-  </si>
-  <si>
-    <t>111121（暂定</t>
-  </si>
-  <si>
-    <t>111122（暂定</t>
-  </si>
-  <si>
-    <t>111123（暂定</t>
-  </si>
-  <si>
-    <t>111124（暂定</t>
-  </si>
-  <si>
-    <t>111125（暂定</t>
-  </si>
-  <si>
-    <t>111126（暂定</t>
-  </si>
-  <si>
-    <t>黑桃A</t>
-  </si>
-  <si>
-    <t>黑桃2</t>
-  </si>
-  <si>
-    <t>黑桃3</t>
-  </si>
-  <si>
-    <t>黑桃4</t>
-  </si>
-  <si>
-    <t>黑桃5</t>
-  </si>
-  <si>
-    <t>黑桃6</t>
-  </si>
-  <si>
-    <t>黑桃7</t>
-  </si>
-  <si>
-    <t>黑桃8</t>
-  </si>
-  <si>
-    <t>黑桃9</t>
-  </si>
-  <si>
-    <t>黑桃10</t>
-  </si>
-  <si>
-    <t>黑桃J</t>
-  </si>
-  <si>
-    <t>黑桃Q</t>
-  </si>
-  <si>
-    <t>黑桃K</t>
-  </si>
-  <si>
-    <t>红桃A</t>
-  </si>
-  <si>
-    <t>红桃2</t>
-  </si>
-  <si>
-    <t>红桃3</t>
-  </si>
-  <si>
-    <t>红桃4</t>
-  </si>
-  <si>
-    <t>红桃5</t>
-  </si>
-  <si>
-    <t>红桃6</t>
-  </si>
-  <si>
-    <t>红桃7</t>
-  </si>
-  <si>
-    <t>红桃8</t>
-  </si>
-  <si>
-    <t>红桃9</t>
-  </si>
-  <si>
-    <t>红桃10</t>
-  </si>
-  <si>
-    <t>红桃J</t>
-  </si>
-  <si>
-    <t>红桃Q</t>
-  </si>
-  <si>
-    <t>红桃K</t>
-  </si>
-  <si>
-    <t>梅花A</t>
-  </si>
-  <si>
-    <t>梅花2</t>
-  </si>
-  <si>
-    <t>梅花3</t>
-  </si>
-  <si>
-    <t>梅花4</t>
-  </si>
-  <si>
-    <t>梅花5</t>
-  </si>
-  <si>
-    <t>梅花6</t>
-  </si>
-  <si>
-    <t>梅花7</t>
-  </si>
-  <si>
-    <t>梅花8</t>
-  </si>
-  <si>
-    <t>梅花9</t>
-  </si>
-  <si>
-    <t>梅花10</t>
-  </si>
-  <si>
-    <t>梅花J</t>
-  </si>
-  <si>
-    <t>梅花Q</t>
-  </si>
-  <si>
-    <t>梅花K</t>
-  </si>
-  <si>
-    <t>方块A</t>
-  </si>
-  <si>
-    <t>方块2</t>
-  </si>
-  <si>
-    <t>方块3</t>
-  </si>
-  <si>
-    <t>方块4</t>
-  </si>
-  <si>
-    <t>方块5</t>
-  </si>
-  <si>
-    <t>方块6</t>
-  </si>
-  <si>
-    <t>方块7</t>
-  </si>
-  <si>
-    <t>方块8</t>
-  </si>
-  <si>
-    <t>方块9</t>
-  </si>
-  <si>
-    <t>方块10</t>
-  </si>
-  <si>
-    <t>方块J</t>
-  </si>
-  <si>
-    <t>方块Q</t>
-  </si>
-  <si>
-    <t>方块K</t>
+    <t>卡牌_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人格牌_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行为标签_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1208,7 +1780,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1230,6 +1802,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1512,16 +2094,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5A527C-B0CB-49B2-B98E-37EF5FCC087B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC77D9CB-E7E9-4C35-B0B9-C7FBCEA4B388}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -1534,27 +2106,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>135</v>
+        <v>500</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -1562,13 +2134,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>242</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -1576,13 +2148,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -1590,13 +2162,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>244</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -1604,13 +2176,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>245</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1618,13 +2190,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>246</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1632,13 +2204,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D8">
         <v>99</v>
@@ -1646,13 +2218,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>248</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -1660,13 +2232,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>249</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1674,13 +2246,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>250</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="D11">
         <v>0.65</v>
@@ -1688,13 +2260,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>251</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="D12">
         <v>0.35</v>
@@ -1702,13 +2274,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>115</v>
+        <v>252</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="D13">
         <v>0.15</v>
@@ -1720,7 +2292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB32D8AA-128F-4460-A9EC-D7D19037C4B3}">
   <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -1743,63 +2315,63 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
-        <v>133</v>
+        <v>501</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>149</v>
+        <v>70</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>150</v>
+        <v>71</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>169</v>
+        <v>87</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>170</v>
+        <v>88</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>196</v>
+        <v>95</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>198</v>
+        <v>97</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>197</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F2">
         <v>550</v>
@@ -1819,19 +2391,19 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F3">
         <v>625</v>
@@ -1851,19 +2423,19 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F4">
         <v>675</v>
@@ -1883,19 +2455,19 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>168</v>
+        <v>507</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1915,19 +2487,19 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F6">
         <v>775</v>
@@ -1947,19 +2519,19 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F7">
         <v>875</v>
@@ -1979,19 +2551,19 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>63</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F8">
         <v>975</v>
@@ -2011,19 +2583,19 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>167</v>
+        <v>508</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2043,19 +2615,19 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F10">
         <v>1050</v>
@@ -2075,19 +2647,19 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F11">
         <v>1275</v>
@@ -2107,19 +2679,19 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F12">
         <v>1475</v>
@@ -2139,19 +2711,19 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>166</v>
+        <v>509</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2171,19 +2743,19 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F14">
         <v>1900</v>
@@ -2210,7 +2782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -2226,7 +2798,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>134</v>
+        <v>502</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2267,7 +2839,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2290,7 +2862,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2313,7 +2885,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2336,7 +2908,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2359,7 +2931,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2382,7 +2954,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2405,7 +2977,7 @@
         <v>7</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2428,7 +3000,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2451,7 +3023,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2474,8 +3046,1399 @@
         <v>10</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9097FB44-50B4-40E5-AF80-97BD251A7399}">
+  <dimension ref="A1:G104"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="16.1640625" customWidth="1"/>
+    <col min="3" max="3" width="19.4140625" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="6" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.9140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G2" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" s="9">
+        <v>2</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" s="9">
+        <v>3</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E5" s="9">
+        <v>4</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G5" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="9">
+        <v>5</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G6" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="9">
+        <v>6</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G7" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="9">
+        <v>7</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G8" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E9" s="9">
+        <v>8</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G9" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E10" s="9">
+        <v>9</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G10" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E11" s="9">
+        <v>10</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G11" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G12" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G13" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G14" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G15" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="9">
+        <v>2</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G16" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" s="9">
+        <v>3</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G17" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" s="9">
+        <v>4</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G18" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E19" s="9">
+        <v>5</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G19" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" s="9">
+        <v>6</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G20" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E21" s="9">
+        <v>7</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G21" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22" s="9">
+        <v>8</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G22" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" s="9">
+        <v>9</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G23" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E24" s="9">
+        <v>10</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G24" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G25" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G26" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G27" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G28" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E29" s="9">
+        <v>2</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G29" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E30" s="9">
+        <v>3</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G30" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E31" s="9">
+        <v>4</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G31" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E32" s="9">
+        <v>5</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G32" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E33" s="9">
+        <v>6</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G33" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E34" s="9">
+        <v>7</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G34" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" s="9">
+        <v>8</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G35" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="9">
+        <v>9</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G36" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E37" s="9">
+        <v>10</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G37" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G38" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G39" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G40" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G41" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E42" s="9">
+        <v>2</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G42" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E43" s="9">
+        <v>3</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G43" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E44" s="9">
+        <v>4</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G44" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E45" s="9">
+        <v>5</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G45" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E46" s="9">
+        <v>6</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G46" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E47" s="9">
+        <v>7</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G47" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E48" s="9">
+        <v>8</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G48" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E49" s="9">
+        <v>9</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G49" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E50" s="9">
+        <v>10</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G50" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G51" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G52" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="G53" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="F54" s="9"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="F55" s="9"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="F56" s="9"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="F57" s="9"/>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="F58" s="9"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="F59" s="9"/>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="F60" s="9"/>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="F61" s="9"/>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="F62" s="9"/>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="F63" s="9"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="F64" s="9"/>
+    </row>
+    <row r="65" spans="6:6">
+      <c r="F65" s="9"/>
+    </row>
+    <row r="66" spans="6:6">
+      <c r="F66" s="9"/>
+    </row>
+    <row r="67" spans="6:6">
+      <c r="F67" s="9"/>
+    </row>
+    <row r="68" spans="6:6">
+      <c r="F68" s="9"/>
+    </row>
+    <row r="69" spans="6:6">
+      <c r="F69" s="9"/>
+    </row>
+    <row r="70" spans="6:6">
+      <c r="F70" s="9"/>
+    </row>
+    <row r="71" spans="6:6">
+      <c r="F71" s="9"/>
+    </row>
+    <row r="72" spans="6:6">
+      <c r="F72" s="9"/>
+    </row>
+    <row r="73" spans="6:6">
+      <c r="F73" s="9"/>
+    </row>
+    <row r="74" spans="6:6">
+      <c r="F74" s="9"/>
+    </row>
+    <row r="75" spans="6:6">
+      <c r="F75" s="9"/>
+    </row>
+    <row r="76" spans="6:6">
+      <c r="F76" s="9"/>
+    </row>
+    <row r="77" spans="6:6">
+      <c r="F77" s="9"/>
+    </row>
+    <row r="78" spans="6:6">
+      <c r="F78" s="9"/>
+    </row>
+    <row r="79" spans="6:6">
+      <c r="F79" s="9"/>
+    </row>
+    <row r="80" spans="6:6">
+      <c r="F80" s="9"/>
+    </row>
+    <row r="81" spans="6:6">
+      <c r="F81" s="9"/>
+    </row>
+    <row r="82" spans="6:6">
+      <c r="F82" s="9"/>
+    </row>
+    <row r="83" spans="6:6">
+      <c r="F83" s="9"/>
+    </row>
+    <row r="84" spans="6:6">
+      <c r="F84" s="9"/>
+    </row>
+    <row r="85" spans="6:6">
+      <c r="F85" s="9"/>
+    </row>
+    <row r="86" spans="6:6">
+      <c r="F86" s="9"/>
+    </row>
+    <row r="87" spans="6:6">
+      <c r="F87" s="9"/>
+    </row>
+    <row r="88" spans="6:6">
+      <c r="F88" s="9"/>
+    </row>
+    <row r="89" spans="6:6">
+      <c r="F89" s="9"/>
+    </row>
+    <row r="90" spans="6:6">
+      <c r="F90" s="9"/>
+    </row>
+    <row r="91" spans="6:6">
+      <c r="F91" s="9"/>
+    </row>
+    <row r="92" spans="6:6">
+      <c r="F92" s="9"/>
+    </row>
+    <row r="93" spans="6:6">
+      <c r="F93" s="9"/>
+    </row>
+    <row r="94" spans="6:6">
+      <c r="F94" s="9"/>
+    </row>
+    <row r="95" spans="6:6">
+      <c r="F95" s="9"/>
+    </row>
+    <row r="96" spans="6:6">
+      <c r="F96" s="9"/>
+    </row>
+    <row r="97" spans="6:6">
+      <c r="F97" s="9"/>
+    </row>
+    <row r="98" spans="6:6">
+      <c r="F98" s="9"/>
+    </row>
+    <row r="99" spans="6:6">
+      <c r="F99" s="9"/>
+    </row>
+    <row r="100" spans="6:6">
+      <c r="F100" s="9"/>
+    </row>
+    <row r="101" spans="6:6">
+      <c r="F101" s="9"/>
+    </row>
+    <row r="102" spans="6:6">
+      <c r="F102" s="9"/>
+    </row>
+    <row r="103" spans="6:6">
+      <c r="F103" s="9"/>
+    </row>
+    <row r="104" spans="6:6">
+      <c r="F104" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2485,7 +4448,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B381E7-3CCD-4BAB-9A3F-F24744709C44}">
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:T35"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -2501,88 +4464,86 @@
     <col min="11" max="11" width="15.9140625" customWidth="1"/>
     <col min="12" max="12" width="18.08203125" customWidth="1"/>
     <col min="14" max="14" width="8.6640625" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:20">
       <c r="A1" s="2" t="s">
-        <v>175</v>
+        <v>504</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>194</v>
+        <v>93</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>213</v>
+        <v>111</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>202</v>
+        <v>505</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>205</v>
+        <v>103</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>206</v>
+        <v>104</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>208</v>
+        <v>106</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2">
-        <v>1001</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" t="s">
+        <v>483</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>265</v>
+        <v>161</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>215</v>
+        <v>112</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="H2" s="4">
         <v>1</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="K2" s="4">
         <v>9</v>
@@ -2592,45 +4553,42 @@
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O2" s="4">
-        <v>1</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3">
-        <v>1002</v>
+        <v>123</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" t="s">
+        <v>484</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>266</v>
+        <v>162</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>216</v>
+        <v>113</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="H3" s="4">
         <v>4</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>232</v>
+        <v>129</v>
       </c>
       <c r="K3" s="4">
         <v>0.9</v>
@@ -2640,45 +4598,42 @@
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O3" s="4">
-        <v>1</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4">
-        <v>1003</v>
+        <v>123</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" t="s">
+        <v>485</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>267</v>
+        <v>163</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="H4" s="4">
         <v>0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>234</v>
+        <v>131</v>
       </c>
       <c r="K4" s="4">
         <v>5</v>
@@ -2688,45 +4643,42 @@
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O4" s="4">
-        <v>1</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5">
-        <v>1004</v>
+        <v>123</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" t="s">
+        <v>486</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>268</v>
+        <v>164</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>218</v>
+        <v>115</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>235</v>
+        <v>132</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="H5" s="4">
         <v>1</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="K5" s="4">
         <v>6</v>
@@ -2736,45 +4688,42 @@
       </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O5" s="4">
-        <v>1</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6">
-        <v>1005</v>
+        <v>123</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" t="s">
+        <v>487</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>269</v>
+        <v>165</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>219</v>
+        <v>116</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="H6" s="4">
         <v>1</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>232</v>
+        <v>129</v>
       </c>
       <c r="K6" s="4">
         <v>1.25</v>
@@ -2784,45 +4733,42 @@
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O6" s="4">
-        <v>1</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7">
-        <v>1006</v>
+        <v>123</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" t="s">
+        <v>488</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>270</v>
+        <v>166</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>236</v>
+        <v>133</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="H7" s="4">
         <v>1</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>237</v>
+        <v>134</v>
       </c>
       <c r="K7" s="4">
         <v>0.25</v>
@@ -2832,45 +4778,42 @@
       </c>
       <c r="M7" s="4"/>
       <c r="N7" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O7" s="4">
-        <v>1</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8">
-        <v>1007</v>
+        <v>123</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" t="s">
+        <v>489</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>271</v>
+        <v>167</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>221</v>
+        <v>118</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>238</v>
+        <v>135</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="H8" s="4">
         <v>1</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>237</v>
+        <v>134</v>
       </c>
       <c r="K8" s="4">
         <v>0.1</v>
@@ -2882,43 +4825,40 @@
       <c r="N8" s="4">
         <v>0.7</v>
       </c>
-      <c r="O8" s="4">
-        <v>1</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9">
-        <v>1008</v>
+      <c r="O8" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" t="s">
+        <v>490</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>272</v>
+        <v>168</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>222</v>
+        <v>119</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>239</v>
+        <v>136</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="H9" s="4">
         <v>1</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -2930,43 +4870,40 @@
       <c r="N9" s="4">
         <v>8</v>
       </c>
-      <c r="O9" s="4">
-        <v>1</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10">
-        <v>1009</v>
+      <c r="O9" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" t="s">
+        <v>491</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>273</v>
+        <v>169</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>223</v>
+        <v>120</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>242</v>
+        <v>139</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="H10" s="4">
         <v>3</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="K10" s="4">
         <v>1.42</v>
@@ -2976,45 +4913,42 @@
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O10" s="4">
-        <v>2</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11">
-        <v>1010</v>
+        <v>123</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" t="s">
+        <v>492</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>274</v>
+        <v>170</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>244</v>
+        <v>378</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>245</v>
+        <v>142</v>
       </c>
       <c r="H11" s="4">
         <v>40</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>232</v>
+        <v>129</v>
       </c>
       <c r="K11" s="4">
         <v>0.78</v>
@@ -3024,45 +4958,42 @@
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O11" s="4">
-        <v>2</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12">
-        <v>1011</v>
+        <v>123</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" t="s">
+        <v>493</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>275</v>
+        <v>171</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>246</v>
+        <v>143</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="H12" s="4">
         <v>2</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="K12" s="4">
         <v>1.36</v>
@@ -3072,45 +5003,42 @@
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O12" s="4">
-        <v>2</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13">
-        <v>1012</v>
+        <v>123</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" t="s">
+        <v>494</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>276</v>
+        <v>172</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="H13" s="4">
         <v>5</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="K13" s="4">
         <v>1.42</v>
@@ -3120,45 +5048,42 @@
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O13" s="4">
-        <v>2</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14">
-        <v>1013</v>
+        <v>123</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" t="s">
+        <v>495</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>277</v>
+        <v>173</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>264</v>
+        <v>160</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>248</v>
+        <v>145</v>
       </c>
       <c r="H14" s="4">
         <v>30</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="K14" s="4">
         <v>2.4500000000000002</v>
@@ -3168,50 +5093,47 @@
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O14" s="4">
-        <v>3</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>229</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15">
-        <v>1014</v>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" t="s">
+        <v>496</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>278</v>
+        <v>174</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>264</v>
+        <v>160</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>242</v>
+        <v>139</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="H15" s="4">
         <v>4</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="K15" s="4">
         <v>3</v>
@@ -3221,50 +5143,47 @@
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O15" s="4">
-        <v>3</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>229</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16">
-        <v>1015</v>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" t="s">
+        <v>497</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>264</v>
+        <v>160</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>250</v>
+        <v>147</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="H16" s="4">
         <v>1</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="K16" s="4">
         <v>2.1</v>
@@ -3274,50 +5193,47 @@
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O16" s="4">
-        <v>3</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>229</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-    </row>
-    <row r="17" spans="1:21">
-      <c r="A17">
-        <v>1016</v>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" t="s">
+        <v>498</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>280</v>
+        <v>176</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>264</v>
+        <v>160</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>259</v>
+        <v>156</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>252</v>
+        <v>149</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="H17" s="4">
         <v>3</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="K17" s="4">
         <v>2.2000000000000002</v>
@@ -3327,21 +5243,18 @@
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O17" s="4">
-        <v>3</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>229</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-    </row>
-    <row r="18" spans="1:21">
+    </row>
+    <row r="18" spans="1:20">
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
@@ -3350,15 +5263,14 @@
       <c r="L18" s="6"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
-      <c r="O18" s="6"/>
+      <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-    </row>
-    <row r="19" spans="1:21">
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -3373,15 +5285,14 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
+      <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-    </row>
-    <row r="20" spans="1:21">
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3402,9 +5313,8 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-    </row>
-    <row r="21" spans="1:21">
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -3425,9 +5335,8 @@
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-    </row>
-    <row r="22" spans="1:21">
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -3448,9 +5357,8 @@
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-    </row>
-    <row r="23" spans="1:21">
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -3471,9 +5379,8 @@
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-    </row>
-    <row r="24" spans="1:21">
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3494,9 +5401,8 @@
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-    </row>
-    <row r="25" spans="1:21">
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -3517,9 +5423,8 @@
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-    </row>
-    <row r="26" spans="1:21">
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -3540,9 +5445,8 @@
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-    </row>
-    <row r="27" spans="1:21">
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -3563,9 +5467,8 @@
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-    </row>
-    <row r="28" spans="1:21">
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -3586,9 +5489,8 @@
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-    </row>
-    <row r="29" spans="1:21">
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -3609,9 +5511,8 @@
       <c r="R29" s="4"/>
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-    </row>
-    <row r="30" spans="1:21">
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -3632,9 +5533,8 @@
       <c r="R30" s="4"/>
       <c r="S30" s="4"/>
       <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-    </row>
-    <row r="31" spans="1:21">
+    </row>
+    <row r="31" spans="1:20">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -3649,9 +5549,8 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-    </row>
-    <row r="32" spans="1:21">
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -3666,9 +5565,8 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-    </row>
-    <row r="33" spans="1:15">
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -3683,9 +5581,8 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-    </row>
-    <row r="34" spans="1:15">
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -3700,9 +5597,8 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-    </row>
-    <row r="35" spans="1:15">
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -3717,7 +5613,6 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3727,19 +5622,414 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7221510-1129-4164-9CB2-A585799E76A4}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="21.75" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="D2" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="D3" s="11">
+        <v>0.38</v>
+      </c>
+      <c r="E3" s="11">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.17</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.03</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.08</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9097FB44-50B4-40E5-AF80-97BD251A7399}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{635BA0DD-5242-4FAF-9723-78A407913F41}">
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="14"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="21.75" customWidth="1"/>
+    <col min="4" max="4" width="16.4140625" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.9140625" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C2">
+        <v>35</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+      <c r="F2">
+        <v>80</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3">
+        <v>35</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+      <c r="F3">
+        <v>80</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C4">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>50</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+      <c r="F4">
+        <v>80</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C5">
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+      <c r="F5">
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C6">
+        <v>35</v>
+      </c>
+      <c r="D6">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+      <c r="F6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+      <c r="F7">
+        <v>80</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8">
+        <v>35</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+      <c r="F8">
+        <v>80</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C9">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+      <c r="F9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3747,856 +6037,1391 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F920F76F-821D-4775-BB25-249DE64C80C4}">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.4140625" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" customWidth="1"/>
-    <col min="3" max="4" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
     <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="19.9140625" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>25</v>
+        <v>506</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>26</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>214</v>
+        <v>481</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>385</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>386</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>388</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>390</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>391</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>392</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>393</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>394</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>395</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>396</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>397</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>398</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>399</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>400</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>401</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>402</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>403</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>404</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>405</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>406</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>407</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>408</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D31" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>409</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D32" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>410</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="D33" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>411</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="D34" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>412</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="D35" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>413</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="D36" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>414</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="D37" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>415</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="D38" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>416</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="D39" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>417</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="D40" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>418</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="D41" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>419</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="D42" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>420</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="D43" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>421</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="D44" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>422</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="D45" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>423</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="D46" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>424</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="D47" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>425</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="D48" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>426</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="D49" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>427</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="D50" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>428</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="D51" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>429</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="D52" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>430</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C53" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="D53" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" t="s">
-        <v>306</v>
-      </c>
-      <c r="C27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" t="s">
-        <v>307</v>
-      </c>
-      <c r="C28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" t="s">
-        <v>308</v>
-      </c>
-      <c r="C29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" t="s">
-        <v>309</v>
-      </c>
-      <c r="C30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" t="s">
-        <v>310</v>
-      </c>
-      <c r="C31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" t="s">
-        <v>311</v>
-      </c>
-      <c r="C32" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" t="s">
-        <v>312</v>
-      </c>
-      <c r="C33" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" t="s">
-        <v>313</v>
-      </c>
-      <c r="C34" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" t="s">
-        <v>314</v>
-      </c>
-      <c r="C35" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" t="s">
-        <v>315</v>
-      </c>
-      <c r="C36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" t="s">
-        <v>316</v>
-      </c>
-      <c r="C37" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" t="s">
-        <v>317</v>
-      </c>
-      <c r="C38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" t="s">
-        <v>318</v>
-      </c>
-      <c r="C39" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" t="s">
-        <v>319</v>
-      </c>
-      <c r="C40" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" t="s">
-        <v>320</v>
-      </c>
-      <c r="C41" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" t="s">
-        <v>321</v>
-      </c>
-      <c r="C42" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" t="s">
-        <v>322</v>
-      </c>
-      <c r="C43" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" t="s">
-        <v>323</v>
-      </c>
-      <c r="C44" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>84</v>
-      </c>
-      <c r="B45" t="s">
-        <v>324</v>
-      </c>
-      <c r="C45" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" t="s">
-        <v>325</v>
-      </c>
-      <c r="C46" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" t="s">
-        <v>326</v>
-      </c>
-      <c r="C47" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" t="s">
-        <v>327</v>
-      </c>
-      <c r="C48" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>88</v>
-      </c>
-      <c r="B49" t="s">
-        <v>328</v>
-      </c>
-      <c r="C49" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>89</v>
-      </c>
-      <c r="B50" t="s">
-        <v>329</v>
-      </c>
-      <c r="C50" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>90</v>
-      </c>
-      <c r="B51" t="s">
-        <v>330</v>
-      </c>
-      <c r="C51" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>91</v>
-      </c>
-      <c r="B52" t="s">
-        <v>331</v>
-      </c>
-      <c r="C52" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>92</v>
-      </c>
-      <c r="B53" t="s">
-        <v>332</v>
-      </c>
-      <c r="C53" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>431</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C54" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="C54" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D54" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>94</v>
+        <v>432</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C55" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="C55" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D55" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>433</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C56" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="C56" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>434</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C57" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="C57" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>435</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C58" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="C58" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D58" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>436</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C59" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="C59" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>437</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C60" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="C60" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D60" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>438</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C61" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="C61" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>101</v>
+        <v>439</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C62" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="C62" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D62" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>440</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C63" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="C63" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>103</v>
-      </c>
-      <c r="C64" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>441</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D64" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>177</v>
-      </c>
-      <c r="C65" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
+        <v>442</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D65" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>178</v>
-      </c>
-      <c r="C66" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>443</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D66" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>179</v>
-      </c>
-      <c r="C67" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
+        <v>444</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D67" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>180</v>
-      </c>
-      <c r="C68" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>445</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D68" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>181</v>
-      </c>
-      <c r="C69" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>446</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D69" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>182</v>
-      </c>
-      <c r="C70" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>447</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D70" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>183</v>
-      </c>
-      <c r="C71" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>448</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D71" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>184</v>
-      </c>
-      <c r="C72" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>449</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D72" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>185</v>
-      </c>
-      <c r="C73" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>450</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D73" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>186</v>
-      </c>
-      <c r="C74" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>451</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D74" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>187</v>
-      </c>
-      <c r="C75" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
+        <v>452</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D75" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>188</v>
-      </c>
-      <c r="C76" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+        <v>453</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D76" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>189</v>
-      </c>
-      <c r="C77" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
+        <v>454</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D77" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>190</v>
-      </c>
-      <c r="C78" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>455</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D78" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>191</v>
-      </c>
-      <c r="C79" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
+        <v>456</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D79" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>192</v>
-      </c>
-      <c r="C80" t="s">
-        <v>29</v>
+        <v>457</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>193</v>
-      </c>
-      <c r="C81" t="s">
-        <v>29</v>
+        <v>458</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>459</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>460</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>461</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>462</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>463</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>464</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>465</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>466</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>467</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>468</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>469</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>470</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>471</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>472</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>473</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>474</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>475</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>476</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>477</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>478</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>479</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>480</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/人格牌.xlsx
+++ b/Docs/人格牌.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29347\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64A2CB5-7FA5-48A3-B237-7582A9F0CE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4F216F-1D6F-465E-9029-EC592AD308FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="894" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="894" firstSheet="8" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全局配置" sheetId="4" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="870">
   <si>
     <t>牌型名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1969,9 +1969,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>出现数量</t>
-  </si>
-  <si>
     <t>出现权重</t>
   </si>
   <si>
@@ -2889,6 +2886,14 @@
   </si>
   <si>
     <t>人格_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单次刷新上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单次抽取数量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3435,7 +3440,7 @@
         <v>149</v>
       </c>
       <c r="B6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -3544,7 +3549,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
@@ -3558,13 +3563,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>681</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>682</v>
       </c>
       <c r="D15" s="30">
         <v>1</v>
@@ -3572,13 +3577,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D16" s="30">
         <v>1</v>
@@ -3586,13 +3591,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>684</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>685</v>
-      </c>
       <c r="C17" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D17" s="30">
         <v>1</v>
@@ -3600,13 +3605,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>686</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>687</v>
-      </c>
       <c r="C18" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D18" s="30">
         <v>1</v>
@@ -3664,73 +3669,73 @@
   <sheetData>
     <row r="1" spans="1:6" s="16" customFormat="1">
       <c r="A1" s="9" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>833</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>832</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>834</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>835</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>836</v>
       </c>
       <c r="F1" s="9"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="25" t="s">
+        <v>836</v>
+      </c>
+      <c r="B2" s="25" t="s">
         <v>837</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="C2" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="C2" s="25" t="s">
-        <v>839</v>
-      </c>
       <c r="D2" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="25" t="s">
+        <v>839</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>840</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="C3" s="25" t="s">
         <v>841</v>
       </c>
-      <c r="C3" s="25" t="s">
-        <v>842</v>
-      </c>
       <c r="D3" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="25" t="s">
+        <v>842</v>
+      </c>
+      <c r="B4" s="25" t="s">
         <v>843</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="C4" s="25" t="s">
         <v>844</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>845</v>
-      </c>
       <c r="D4" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="8"/>
     </row>
@@ -3752,39 +3757,39 @@
   <sheetData>
     <row r="1" spans="1:8" s="23" customFormat="1">
       <c r="A1" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>847</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>832</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>848</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>849</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>850</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>851</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="18" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>562</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D2" s="8">
         <v>15</v>
@@ -3804,13 +3809,13 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="18" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>413</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
@@ -3836,7 +3841,7 @@
         <v>232</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D4" s="8">
         <v>40</v>
@@ -3862,7 +3867,7 @@
         <v>233</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D5" s="8">
         <v>30</v>
@@ -3888,7 +3893,7 @@
         <v>234</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D6" s="8">
         <v>1</v>
@@ -3914,7 +3919,7 @@
         <v>235</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D7" s="8">
         <v>20</v>
@@ -3940,7 +3945,7 @@
         <v>236</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D8" s="8">
         <v>20</v>
@@ -3966,7 +3971,7 @@
         <v>237</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D9" s="31">
         <v>0.05</v>
@@ -4005,19 +4010,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="23" customFormat="1">
       <c r="A1" s="26" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B1" s="26" t="s">
+        <v>788</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>789</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="D1" s="26" t="s">
         <v>790</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="E1" s="26" t="s">
         <v>791</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>792</v>
       </c>
       <c r="F1" s="26" t="s">
         <v>500</v>
@@ -4025,16 +4030,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E2" s="6">
         <v>5</v>
@@ -4045,16 +4050,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="6" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E3" s="6">
         <v>10</v>
@@ -4065,16 +4070,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="6" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E4" s="6">
         <v>15</v>
@@ -4085,16 +4090,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E5" s="6">
         <v>20</v>
@@ -4105,16 +4110,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>142</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E6" s="6">
         <v>5</v>
@@ -4125,16 +4130,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>142</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E7" s="6">
         <v>10</v>
@@ -4145,16 +4150,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>142</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E8" s="6">
         <v>15</v>
@@ -4165,16 +4170,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>142</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E9" s="6">
         <v>20</v>
@@ -4185,16 +4190,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>143</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E10" s="6">
         <v>5</v>
@@ -4205,16 +4210,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>143</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E11" s="6">
         <v>10</v>
@@ -4225,16 +4230,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>143</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E12" s="6">
         <v>15</v>
@@ -4245,16 +4250,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>143</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E13" s="6">
         <v>20</v>
@@ -4265,16 +4270,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E14" s="6">
         <v>5</v>
@@ -4285,16 +4290,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E15" s="6">
         <v>10</v>
@@ -4305,16 +4310,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E16" s="6">
         <v>15</v>
@@ -4325,16 +4330,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E17" s="6">
         <v>20</v>
@@ -4366,22 +4371,22 @@
   <sheetData>
     <row r="1" spans="1:16" s="33" customFormat="1">
       <c r="A1" s="32" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B1" s="32" t="s">
+        <v>738</v>
+      </c>
+      <c r="C1" s="32" t="s">
         <v>739</v>
       </c>
-      <c r="C1" s="32" t="s">
-        <v>740</v>
-      </c>
       <c r="D1" s="9" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E1" s="32" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F1" s="32" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G1" s="32" t="s">
         <v>500</v>
@@ -4393,16 +4398,16 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>752</v>
-      </c>
       <c r="C2" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E2" s="4">
         <v>61</v>
@@ -4420,16 +4425,16 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E3" s="4">
         <v>67</v>
@@ -4447,16 +4452,16 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="6" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E4" s="4">
         <v>73</v>
@@ -4474,16 +4479,16 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E5" s="4">
         <v>79</v>
@@ -4501,16 +4506,16 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="6" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E6" s="4">
         <v>53</v>
@@ -4528,16 +4533,16 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="6" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E7" s="4">
         <v>58</v>
@@ -4555,16 +4560,16 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="6" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E8" s="4">
         <v>63</v>
@@ -4582,16 +4587,16 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="6" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E9" s="4">
         <v>68</v>
@@ -4609,16 +4614,16 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="6" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E10" s="4">
         <v>57</v>
@@ -4636,16 +4641,16 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="6" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E11" s="4">
         <v>62</v>
@@ -4663,16 +4668,16 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E12" s="4">
         <v>67</v>
@@ -4690,16 +4695,16 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E13" s="4">
         <v>72</v>
@@ -4717,16 +4722,16 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="6" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E14" s="4">
         <v>63</v>
@@ -4744,16 +4749,16 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="6" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E15" s="4">
         <v>69</v>
@@ -4771,16 +4776,16 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="6" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E16" s="4">
         <v>75</v>
@@ -4798,16 +4803,16 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E17" s="4">
         <v>81</v>
@@ -4825,16 +4830,16 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="6" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E18" s="4">
         <v>66</v>
@@ -4852,16 +4857,16 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E19" s="4">
         <v>72</v>
@@ -4879,16 +4884,16 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E20" s="4">
         <v>78</v>
@@ -4906,16 +4911,16 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E21" s="4">
         <v>84</v>
@@ -4933,16 +4938,16 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E22" s="4">
         <v>72</v>
@@ -4960,16 +4965,16 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E23" s="4">
         <v>79</v>
@@ -4987,16 +4992,16 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="6" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E24" s="4">
         <v>86</v>
@@ -5014,16 +5019,16 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E25" s="4">
         <v>93</v>
@@ -5041,16 +5046,16 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="6" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E26" s="4">
         <v>81</v>
@@ -5068,16 +5073,16 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E27" s="4">
         <v>88</v>
@@ -5095,16 +5100,16 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E28" s="4">
         <v>95</v>
@@ -5122,16 +5127,16 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E29" s="4">
         <v>102</v>
@@ -5149,16 +5154,16 @@
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E30" s="4">
         <v>110</v>
@@ -5176,16 +5181,16 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E31" s="4">
         <v>120</v>
@@ -5203,16 +5208,16 @@
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E32" s="4">
         <v>130</v>
@@ -5230,16 +5235,16 @@
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E33" s="4">
         <v>140</v>
@@ -5257,16 +5262,16 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E34" s="4">
         <v>105</v>
@@ -5284,16 +5289,16 @@
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="6" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E35" s="4">
         <v>115</v>
@@ -5311,16 +5316,16 @@
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="6" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E36" s="4">
         <v>125</v>
@@ -5338,16 +5343,16 @@
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="6" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E37" s="4">
         <v>135</v>
@@ -5365,16 +5370,16 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="C38" s="18" t="s">
         <v>786</v>
       </c>
-      <c r="C38" s="18" t="s">
-        <v>787</v>
-      </c>
       <c r="D38" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E38" s="4">
         <v>77</v>
@@ -5392,16 +5397,16 @@
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="6" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B39" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="C39" s="18" t="s">
         <v>786</v>
       </c>
-      <c r="C39" s="18" t="s">
-        <v>787</v>
-      </c>
       <c r="D39" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E39" s="4">
         <v>84</v>
@@ -5419,16 +5424,16 @@
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="6" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="C40" s="18" t="s">
         <v>786</v>
       </c>
-      <c r="C40" s="18" t="s">
-        <v>787</v>
-      </c>
       <c r="D40" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E40" s="4">
         <v>91</v>
@@ -5446,16 +5451,16 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B41" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="C41" s="18" t="s">
         <v>786</v>
       </c>
-      <c r="C41" s="18" t="s">
-        <v>787</v>
-      </c>
       <c r="D41" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E41" s="4">
         <v>98</v>
@@ -5473,7 +5478,7 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>451</v>
@@ -5482,7 +5487,7 @@
         <v>494</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E42" s="4">
         <v>110</v>
@@ -5500,7 +5505,7 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>451</v>
@@ -5509,7 +5514,7 @@
         <v>494</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E43" s="4">
         <v>120</v>
@@ -5527,7 +5532,7 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>451</v>
@@ -5536,7 +5541,7 @@
         <v>494</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E44" s="4">
         <v>130</v>
@@ -5554,7 +5559,7 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>451</v>
@@ -5563,7 +5568,7 @@
         <v>494</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E45" s="4">
         <v>140</v>
@@ -5587,7 +5592,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{695D6A22-B2FC-4A7F-B8D1-3EAF8ABD09E0}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -5597,21 +5602,21 @@
   <sheetData>
     <row r="1" spans="1:3" s="16" customFormat="1">
       <c r="A1" s="26" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
@@ -5619,7 +5624,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B3" s="25" t="s">
         <v>510</v>
@@ -5630,7 +5635,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>511</v>
@@ -5641,7 +5646,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>512</v>
@@ -5652,7 +5657,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>513</v>
@@ -5663,7 +5668,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>514</v>
@@ -5674,7 +5679,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>515</v>
@@ -5685,7 +5690,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>516</v>
@@ -5696,7 +5701,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>517</v>
@@ -5707,7 +5712,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>518</v>
@@ -5718,7 +5723,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>519</v>
@@ -5729,7 +5734,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="13" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>520</v>
@@ -5740,7 +5745,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="13" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>521</v>
@@ -5751,7 +5756,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="13" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B15" s="25" t="s">
         <v>522</v>
@@ -5762,7 +5767,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="13" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B16" s="25" t="s">
         <v>523</v>
@@ -5773,7 +5778,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="13" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>524</v>
@@ -5784,7 +5789,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="13" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B18" s="25" t="s">
         <v>525</v>
@@ -5795,7 +5800,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="13" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B19" s="25" t="s">
         <v>526</v>
@@ -5806,7 +5811,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="13" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B20" s="25" t="s">
         <v>527</v>
@@ -5817,7 +5822,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="13" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B21" s="25" t="s">
         <v>528</v>
@@ -5828,7 +5833,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="13" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B22" s="25" t="s">
         <v>529</v>
@@ -5839,7 +5844,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B23" s="25" t="s">
         <v>530</v>
@@ -5850,7 +5855,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="13" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B24" s="25" t="s">
         <v>531</v>
@@ -5861,7 +5866,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="13" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B25" s="25" t="s">
         <v>532</v>
@@ -5872,7 +5877,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="13" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B26" s="25" t="s">
         <v>533</v>
@@ -5883,7 +5888,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="13" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B27" s="25" t="s">
         <v>534</v>
@@ -5894,7 +5899,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="13" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B28" s="25" t="s">
         <v>535</v>
@@ -5905,7 +5910,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="13" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B29" s="25" t="s">
         <v>536</v>
@@ -5916,7 +5921,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="13" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B30" s="25" t="s">
         <v>537</v>
@@ -5927,7 +5932,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="13" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B31" s="25" t="s">
         <v>538</v>
@@ -5938,7 +5943,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="13" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B32" s="25" t="s">
         <v>539</v>
@@ -5949,7 +5954,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="13" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B33" s="25" t="s">
         <v>540</v>
@@ -5960,7 +5965,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="13" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B34" s="25" t="s">
         <v>541</v>
@@ -5971,7 +5976,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="13" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B35" s="25" t="s">
         <v>542</v>
@@ -5982,7 +5987,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B36" s="25" t="s">
         <v>543</v>
@@ -5993,7 +5998,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="13" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B37" s="25" t="s">
         <v>544</v>
@@ -6004,7 +6009,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="13" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B38" s="25" t="s">
         <v>545</v>
@@ -6015,7 +6020,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="13" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B39" s="25" t="s">
         <v>546</v>
@@ -6026,7 +6031,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="13" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B40" s="25" t="s">
         <v>547</v>
@@ -6037,7 +6042,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="13" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B41" s="25" t="s">
         <v>548</v>
@@ -6048,7 +6053,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="13" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B42" s="25" t="s">
         <v>549</v>
@@ -6059,7 +6064,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="13" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B43" s="25" t="s">
         <v>550</v>
@@ -6070,7 +6075,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="13" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B44" s="25" t="s">
         <v>551</v>
@@ -6081,7 +6086,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="13" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B45" s="25" t="s">
         <v>552</v>
@@ -6092,7 +6097,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="13" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B46" s="25" t="s">
         <v>553</v>
@@ -6103,7 +6108,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B47" s="25" t="s">
         <v>554</v>
@@ -6114,7 +6119,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="13" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B48" s="25" t="s">
         <v>555</v>
@@ -6125,7 +6130,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B49" s="25" t="s">
         <v>556</v>
@@ -6136,7 +6141,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="13" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B50" s="25" t="s">
         <v>557</v>
@@ -6147,7 +6152,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B51" s="25" t="s">
         <v>558</v>
@@ -6158,7 +6163,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="13" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B52" s="25" t="s">
         <v>559</v>
@@ -6169,7 +6174,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B53" s="25" t="s">
         <v>560</v>
@@ -6180,145 +6185,178 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="13" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C54" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="13" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B55" s="13" t="s">
         <v>563</v>
       </c>
       <c r="C55" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="13" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>564</v>
       </c>
       <c r="C56" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="13" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B57" s="13" t="s">
         <v>565</v>
       </c>
       <c r="C57" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="13" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B58" s="13" t="s">
         <v>566</v>
       </c>
       <c r="C58" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="13" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B59" s="13" t="s">
         <v>567</v>
       </c>
       <c r="C59" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="13" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>568</v>
       </c>
       <c r="C60" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="13" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B61" s="13" t="s">
         <v>569</v>
       </c>
       <c r="C61" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="13" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C62" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="13" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C63" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="13" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C64" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="13" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C65" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="13" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C66" s="4">
-        <v>20</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="13" t="s">
+        <v>716</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>716</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="13" t="s">
+        <v>717</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>717</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="13" t="s">
+        <v>718</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>718</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6329,39 +6367,42 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02162BC-2467-45CC-992C-0AA464A18721}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16.75" style="29" customWidth="1"/>
     <col min="2" max="2" width="15.4140625" style="29" customWidth="1"/>
     <col min="3" max="3" width="15.5" style="29" customWidth="1"/>
-    <col min="4" max="4" width="14.9140625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.9140625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="29.08203125" style="29" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="29"/>
+    <col min="4" max="5" width="14.9140625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="15.9140625" style="29" customWidth="1"/>
+    <col min="7" max="7" width="29.08203125" style="29" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="23" customFormat="1">
+    <row r="1" spans="1:7" s="23" customFormat="1">
       <c r="A1" s="9" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>499</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>868</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="25" t="s">
         <v>585</v>
-      </c>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="25" t="s">
-        <v>586</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>346</v>
@@ -6373,13 +6414,16 @@
         <v>1</v>
       </c>
       <c r="E2" s="8">
-        <v>45</v>
-      </c>
-      <c r="F2" s="25"/>
-    </row>
-    <row r="3" spans="1:6">
+        <v>4</v>
+      </c>
+      <c r="F2" s="8">
+        <v>40</v>
+      </c>
+      <c r="G2" s="25"/>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="25" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B3" s="28" t="s">
         <v>346</v>
@@ -6391,13 +6435,16 @@
         <v>1</v>
       </c>
       <c r="E3" s="8">
-        <v>20</v>
-      </c>
-      <c r="F3" s="25"/>
-    </row>
-    <row r="4" spans="1:6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8">
+        <v>8</v>
+      </c>
+      <c r="G3" s="25"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="25" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B4" s="28" t="s">
         <v>346</v>
@@ -6409,13 +6456,16 @@
         <v>1</v>
       </c>
       <c r="E4" s="8">
-        <v>35</v>
-      </c>
-      <c r="F4" s="25"/>
-    </row>
-    <row r="5" spans="1:6">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8">
+        <v>52</v>
+      </c>
+      <c r="G4" s="25"/>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="25" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B5" s="28" t="s">
         <v>347</v>
@@ -6427,13 +6477,16 @@
         <v>1</v>
       </c>
       <c r="E5" s="8">
-        <v>40</v>
-      </c>
-      <c r="F5" s="25"/>
-    </row>
-    <row r="6" spans="1:6">
+        <v>4</v>
+      </c>
+      <c r="F5" s="8">
+        <v>35</v>
+      </c>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="25" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B6" s="28" t="s">
         <v>347</v>
@@ -6445,13 +6498,16 @@
         <v>1</v>
       </c>
       <c r="E6" s="8">
-        <v>25</v>
-      </c>
-      <c r="F6" s="25"/>
-    </row>
-    <row r="7" spans="1:6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
+        <v>10</v>
+      </c>
+      <c r="G6" s="25"/>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="25" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B7" s="28" t="s">
         <v>347</v>
@@ -6463,13 +6519,16 @@
         <v>1</v>
       </c>
       <c r="E7" s="8">
-        <v>35</v>
-      </c>
-      <c r="F7" s="25"/>
-    </row>
-    <row r="8" spans="1:6">
+        <v>4</v>
+      </c>
+      <c r="F7" s="8">
+        <v>55</v>
+      </c>
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="25" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>348</v>
@@ -6481,13 +6540,16 @@
         <v>1</v>
       </c>
       <c r="E8" s="8">
+        <v>4</v>
+      </c>
+      <c r="F8" s="8">
         <v>30</v>
       </c>
-      <c r="F8" s="25"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="25"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="25" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B9" s="28" t="s">
         <v>348</v>
@@ -6499,13 +6561,16 @@
         <v>1</v>
       </c>
       <c r="E9" s="8">
-        <v>30</v>
-      </c>
-      <c r="F9" s="25"/>
-    </row>
-    <row r="10" spans="1:6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8">
+        <v>12</v>
+      </c>
+      <c r="G9" s="25"/>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="25" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B10" s="28" t="s">
         <v>348</v>
@@ -6517,9 +6582,12 @@
         <v>1</v>
       </c>
       <c r="E10" s="8">
-        <v>40</v>
-      </c>
-      <c r="F10" s="25"/>
+        <v>4</v>
+      </c>
+      <c r="F10" s="8">
+        <v>58</v>
+      </c>
+      <c r="G10" s="25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6546,7 +6614,7 @@
         <v>505</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D1" s="9"/>
     </row>
@@ -6558,7 +6626,7 @@
         <v>582</v>
       </c>
       <c r="C2" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="25"/>
     </row>
@@ -6570,7 +6638,7 @@
         <v>583</v>
       </c>
       <c r="C3" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" s="25"/>
     </row>
@@ -6649,15 +6717,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="23" customFormat="1">
       <c r="A1" s="26" t="s">
+        <v>788</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>789</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>137</v>
@@ -6665,7 +6733,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>142</v>
@@ -6673,7 +6741,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>143</v>
@@ -6681,7 +6749,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>144</v>
@@ -6849,7 +6917,7 @@
         <v>59</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>73</v>
@@ -6890,7 +6958,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E2" t="s">
         <v>75</v>
@@ -6911,10 +6979,10 @@
         <v>352</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -6931,7 +6999,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E3" t="s">
         <v>75</v>
@@ -6952,10 +7020,10 @@
         <v>352</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -6972,7 +7040,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E4" t="s">
         <v>75</v>
@@ -6993,10 +7061,10 @@
         <v>352</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -7013,7 +7081,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E5" t="s">
         <v>76</v>
@@ -7037,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -7054,7 +7122,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E6" t="s">
         <v>75</v>
@@ -7075,10 +7143,10 @@
         <v>352</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -7095,7 +7163,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E7" t="s">
         <v>75</v>
@@ -7116,10 +7184,10 @@
         <v>352</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -7136,7 +7204,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E8" t="s">
         <v>75</v>
@@ -7157,10 +7225,10 @@
         <v>352</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -7177,7 +7245,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E9" t="s">
         <v>76</v>
@@ -7201,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -7218,7 +7286,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E10" t="s">
         <v>75</v>
@@ -7239,10 +7307,10 @@
         <v>352</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -7259,7 +7327,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E11" t="s">
         <v>75</v>
@@ -7280,10 +7348,10 @@
         <v>352</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -7300,7 +7368,7 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E12" t="s">
         <v>75</v>
@@ -7321,10 +7389,10 @@
         <v>352</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -7341,7 +7409,7 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E13" t="s">
         <v>76</v>
@@ -7365,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="M13">
         <v>1</v>
@@ -7382,7 +7450,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E14" t="s">
         <v>75</v>
@@ -7403,27 +7471,27 @@
         <v>352</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F15">
         <v>2500</v>
@@ -7441,10 +7509,10 @@
         <v>352</v>
       </c>
       <c r="K15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -7452,19 +7520,19 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E16" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F16">
         <v>2750</v>
@@ -7482,10 +7550,10 @@
         <v>352</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L16" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -7493,19 +7561,19 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E17" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -7526,7 +7594,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -7534,19 +7602,19 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E18" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F18">
         <v>3200</v>
@@ -7567,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -7597,10 +7665,10 @@
         <v>345</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>676</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>677</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>26</v>
@@ -8427,7 +8495,7 @@
         <v>312</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>212</v>
@@ -8468,10 +8536,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>218</v>
@@ -8482,7 +8550,7 @@
         <v>316</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>218</v>
@@ -8493,7 +8561,7 @@
         <v>317</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>218</v>
@@ -8504,7 +8572,7 @@
         <v>318</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>218</v>
@@ -8515,7 +8583,7 @@
         <v>319</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>218</v>
@@ -8526,7 +8594,7 @@
         <v>320</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>218</v>
@@ -8537,7 +8605,7 @@
         <v>321</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>218</v>
@@ -8548,7 +8616,7 @@
         <v>322</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>218</v>
@@ -8559,7 +8627,7 @@
         <v>323</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>218</v>
@@ -8570,7 +8638,7 @@
         <v>324</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>218</v>
@@ -8581,7 +8649,7 @@
         <v>325</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>218</v>
@@ -8592,7 +8660,7 @@
         <v>326</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>218</v>
@@ -8603,7 +8671,7 @@
         <v>327</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>218</v>
@@ -8614,7 +8682,7 @@
         <v>328</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>218</v>
@@ -8625,7 +8693,7 @@
         <v>329</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>218</v>
@@ -8636,7 +8704,7 @@
         <v>330</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C95" s="7" t="s">
         <v>218</v>
@@ -8655,7 +8723,7 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>64</v>
@@ -8666,7 +8734,7 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>221</v>
@@ -8677,7 +8745,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>222</v>
@@ -8688,7 +8756,7 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>223</v>
@@ -8699,7 +8767,7 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>224</v>
@@ -8710,7 +8778,7 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>225</v>
@@ -8721,7 +8789,7 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>226</v>
@@ -8732,7 +8800,7 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>227</v>
@@ -8743,7 +8811,7 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>228</v>
@@ -8774,7 +8842,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="16" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -9091,10 +9159,10 @@
         <v>25</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>135</v>
@@ -9117,10 +9185,10 @@
         <v>136</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>138</v>
@@ -9143,10 +9211,10 @@
         <v>136</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F3" s="8">
         <v>2</v>
@@ -9169,10 +9237,10 @@
         <v>136</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F4" s="8">
         <v>3</v>
@@ -9195,10 +9263,10 @@
         <v>136</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F5" s="8">
         <v>4</v>
@@ -9221,10 +9289,10 @@
         <v>136</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F6" s="8">
         <v>5</v>
@@ -9247,10 +9315,10 @@
         <v>136</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F7" s="8">
         <v>6</v>
@@ -9273,10 +9341,10 @@
         <v>136</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F8" s="8">
         <v>7</v>
@@ -9299,10 +9367,10 @@
         <v>136</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F9" s="8">
         <v>8</v>
@@ -9325,10 +9393,10 @@
         <v>136</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F10" s="8">
         <v>9</v>
@@ -9351,10 +9419,10 @@
         <v>136</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F11" s="8">
         <v>10</v>
@@ -9377,10 +9445,10 @@
         <v>136</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>139</v>
@@ -9403,10 +9471,10 @@
         <v>136</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>140</v>
@@ -9429,10 +9497,10 @@
         <v>136</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>141</v>
@@ -9455,10 +9523,10 @@
         <v>136</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>138</v>
@@ -9481,10 +9549,10 @@
         <v>136</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F16" s="8">
         <v>2</v>
@@ -9507,10 +9575,10 @@
         <v>136</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F17" s="8">
         <v>3</v>
@@ -9533,10 +9601,10 @@
         <v>136</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F18" s="8">
         <v>4</v>
@@ -9559,10 +9627,10 @@
         <v>136</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F19" s="8">
         <v>5</v>
@@ -9585,10 +9653,10 @@
         <v>136</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F20" s="8">
         <v>6</v>
@@ -9611,10 +9679,10 @@
         <v>136</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F21" s="8">
         <v>7</v>
@@ -9637,10 +9705,10 @@
         <v>136</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F22" s="8">
         <v>8</v>
@@ -9663,10 +9731,10 @@
         <v>136</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F23" s="8">
         <v>9</v>
@@ -9689,10 +9757,10 @@
         <v>136</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F24" s="8">
         <v>10</v>
@@ -9715,10 +9783,10 @@
         <v>136</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>139</v>
@@ -9735,16 +9803,16 @@
         <v>181</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>136</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>140</v>
@@ -9767,10 +9835,10 @@
         <v>136</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>141</v>
@@ -9793,10 +9861,10 @@
         <v>136</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>138</v>
@@ -9819,10 +9887,10 @@
         <v>136</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F29" s="8">
         <v>2</v>
@@ -9845,10 +9913,10 @@
         <v>136</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F30" s="8">
         <v>3</v>
@@ -9871,10 +9939,10 @@
         <v>136</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F31" s="8">
         <v>4</v>
@@ -9897,10 +9965,10 @@
         <v>136</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F32" s="8">
         <v>5</v>
@@ -9923,10 +9991,10 @@
         <v>136</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F33" s="8">
         <v>6</v>
@@ -9949,10 +10017,10 @@
         <v>136</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F34" s="8">
         <v>7</v>
@@ -9975,10 +10043,10 @@
         <v>136</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F35" s="8">
         <v>8</v>
@@ -10001,10 +10069,10 @@
         <v>136</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F36" s="8">
         <v>9</v>
@@ -10027,10 +10095,10 @@
         <v>136</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F37" s="8">
         <v>10</v>
@@ -10053,10 +10121,10 @@
         <v>136</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>139</v>
@@ -10079,10 +10147,10 @@
         <v>136</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>140</v>
@@ -10105,10 +10173,10 @@
         <v>136</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>141</v>
@@ -10131,10 +10199,10 @@
         <v>136</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>138</v>
@@ -10157,10 +10225,10 @@
         <v>136</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F42" s="8">
         <v>2</v>
@@ -10183,10 +10251,10 @@
         <v>136</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F43" s="8">
         <v>3</v>
@@ -10209,10 +10277,10 @@
         <v>136</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F44" s="8">
         <v>4</v>
@@ -10235,10 +10303,10 @@
         <v>136</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F45" s="8">
         <v>5</v>
@@ -10261,10 +10329,10 @@
         <v>136</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F46" s="8">
         <v>6</v>
@@ -10287,10 +10355,10 @@
         <v>136</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F47" s="8">
         <v>7</v>
@@ -10313,10 +10381,10 @@
         <v>136</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F48" s="8">
         <v>8</v>
@@ -10339,10 +10407,10 @@
         <v>136</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F49" s="8">
         <v>9</v>
@@ -10365,10 +10433,10 @@
         <v>136</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F50" s="8">
         <v>10</v>
@@ -10391,10 +10459,10 @@
         <v>136</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>139</v>
@@ -10417,10 +10485,10 @@
         <v>136</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>140</v>
@@ -10443,13 +10511,13 @@
         <v>136</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>211</v>
@@ -12930,9 +12998,9 @@
     <col min="3" max="3" width="10.4140625" customWidth="1"/>
     <col min="4" max="4" width="8.58203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="9.4140625" customWidth="1"/>
     <col min="7" max="7" width="12.4140625" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12944,7 +13012,7 @@
         <v>498</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D1" s="27" t="s">
         <v>500</v>
@@ -12965,7 +13033,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="18" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>82</v>
@@ -13307,7 +13375,7 @@
         <v>96</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D16" s="18">
         <v>2</v>
@@ -14222,7 +14290,7 @@
         <v>580</v>
       </c>
       <c r="D54" s="18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E54" s="18">
         <v>1</v>
@@ -14246,7 +14314,7 @@
         <v>580</v>
       </c>
       <c r="D55" s="18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E55" s="18">
         <v>1</v>
@@ -14270,7 +14338,7 @@
         <v>580</v>
       </c>
       <c r="D56" s="18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E56" s="18">
         <v>1</v>
@@ -14294,7 +14362,7 @@
         <v>580</v>
       </c>
       <c r="D57" s="18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E57" s="18">
         <v>1</v>
@@ -14318,7 +14386,7 @@
         <v>580</v>
       </c>
       <c r="D58" s="18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E58" s="18">
         <v>1</v>
@@ -14342,7 +14410,7 @@
         <v>580</v>
       </c>
       <c r="D59" s="18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E59" s="18">
         <v>1</v>
@@ -14366,7 +14434,7 @@
         <v>580</v>
       </c>
       <c r="D60" s="18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E60" s="18">
         <v>1</v>
@@ -14390,7 +14458,7 @@
         <v>580</v>
       </c>
       <c r="D61" s="18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E61" s="18">
         <v>1</v>
@@ -14405,7 +14473,7 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="13" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B62" s="18" t="s">
         <v>570</v>
@@ -14414,7 +14482,7 @@
         <v>509</v>
       </c>
       <c r="D62" s="18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E62" s="18">
         <v>1</v>
@@ -14432,7 +14500,7 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B63" s="18" t="s">
         <v>571</v>
@@ -14441,7 +14509,7 @@
         <v>509</v>
       </c>
       <c r="D63" s="18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E63" s="18">
         <v>1</v>
@@ -14459,7 +14527,7 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>572</v>
@@ -14468,7 +14536,7 @@
         <v>509</v>
       </c>
       <c r="D64" s="18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E64" s="18">
         <v>1</v>
@@ -14486,7 +14554,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B65" s="18" t="s">
         <v>573</v>
@@ -14495,7 +14563,7 @@
         <v>509</v>
       </c>
       <c r="D65" s="18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E65" s="18">
         <v>1</v>
@@ -14513,7 +14581,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B66" s="18" t="s">
         <v>574</v>
@@ -14537,80 +14605,80 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="13" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C67" s="18" t="s">
         <v>509</v>
       </c>
       <c r="D67" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
       </c>
       <c r="F67" s="18" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="13" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>509</v>
       </c>
       <c r="D68" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
       </c>
       <c r="F68" s="18" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C69" s="18" t="s">
         <v>509</v>
       </c>
       <c r="D69" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="71" spans="1:9">

--- a/Docs/人格牌.xlsx
+++ b/Docs/人格牌.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="718">
   <si>
     <t>牌型名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2369,6 +2369,30 @@
   <si>
     <t>关卡类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>终局观察者</t>
+  </si>
+  <si>
+    <t>克制的赌徒</t>
+  </si>
+  <si>
+    <t>结构收藏家</t>
+  </si>
+  <si>
+    <t>隐境寻路者</t>
+  </si>
+  <si>
+    <t>断舍离者</t>
+  </si>
+  <si>
+    <t>善变漫游者</t>
+  </si>
+  <si>
+    <t>留手谋划者</t>
+  </si>
+  <si>
+    <t>满手承诺者</t>
   </si>
 </sst>
 </file>
@@ -4934,7 +4958,7 @@
         <v>320</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>241</v>
+        <v>710</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>224</v>
@@ -4945,7 +4969,7 @@
         <v>321</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>242</v>
+        <v>711</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>224</v>
@@ -4956,7 +4980,7 @@
         <v>322</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>243</v>
+        <v>712</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>224</v>
@@ -4967,7 +4991,7 @@
         <v>323</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>244</v>
+        <v>713</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>224</v>
@@ -4978,7 +5002,7 @@
         <v>324</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>245</v>
+        <v>714</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>224</v>
@@ -4989,7 +5013,7 @@
         <v>325</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>246</v>
+        <v>715</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>224</v>
@@ -5000,7 +5024,7 @@
         <v>326</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>247</v>
+        <v>716</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>224</v>
@@ -5011,7 +5035,7 @@
         <v>327</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>248</v>
+        <v>717</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>224</v>
@@ -7701,7 +7725,7 @@
         <v>360</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>241</v>
+        <v>710</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>424</v>
@@ -7736,7 +7760,7 @@
         <v>361</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>242</v>
+        <v>711</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>425</v>
@@ -7771,7 +7795,7 @@
         <v>362</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>243</v>
+        <v>712</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>426</v>
@@ -7806,7 +7830,7 @@
         <v>363</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>244</v>
+        <v>713</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>427</v>
@@ -7841,7 +7865,7 @@
         <v>364</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>245</v>
+        <v>714</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>428</v>
@@ -7876,7 +7900,7 @@
         <v>365</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>246</v>
+        <v>715</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>429</v>
@@ -7911,7 +7935,7 @@
         <v>366</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>247</v>
+        <v>716</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>430</v>
@@ -7946,7 +7970,7 @@
         <v>367</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>248</v>
+        <v>717</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>431</v>
@@ -8570,7 +8594,7 @@
     </row>
     <row r="2" spans="1:5" ht="13" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>381</v>
+        <v>424</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>408</v>
@@ -8587,7 +8611,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>382</v>
+        <v>425</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>405</v>
@@ -8604,7 +8628,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>509</v>
@@ -8621,7 +8645,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>384</v>
+        <v>427</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>406</v>
@@ -8638,7 +8662,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>385</v>
+        <v>428</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>407</v>
@@ -8655,7 +8679,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>386</v>
+        <v>429</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>461</v>
@@ -8672,7 +8696,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>387</v>
+        <v>430</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>460</v>
@@ -8689,7 +8713,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
-        <v>388</v>
+        <v>431</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>508</v>
@@ -8994,7 +9018,7 @@
         <v>389</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>241</v>
+        <v>710</v>
       </c>
       <c r="C2" s="6">
         <v>40</v>
@@ -9019,7 +9043,7 @@
         <v>393</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>241</v>
+        <v>710</v>
       </c>
       <c r="C3" s="6">
         <v>25</v>
@@ -9044,7 +9068,7 @@
         <v>391</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>241</v>
+        <v>710</v>
       </c>
       <c r="C4" s="6">
         <v>20</v>
@@ -9069,7 +9093,7 @@
         <v>390</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>241</v>
+        <v>710</v>
       </c>
       <c r="C5" s="6">
         <v>10</v>
@@ -9094,7 +9118,7 @@
         <v>392</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>241</v>
+        <v>710</v>
       </c>
       <c r="C6" s="6">
         <v>5</v>
@@ -9119,7 +9143,7 @@
         <v>394</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>242</v>
+        <v>711</v>
       </c>
       <c r="C7" s="6">
         <v>35</v>
@@ -9144,7 +9168,7 @@
         <v>395</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>242</v>
+        <v>711</v>
       </c>
       <c r="C8" s="6">
         <v>30</v>
@@ -9169,7 +9193,7 @@
         <v>396</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>442</v>
+        <v>711</v>
       </c>
       <c r="C9" s="6">
         <v>20</v>
@@ -9194,7 +9218,7 @@
         <v>397</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>442</v>
+        <v>711</v>
       </c>
       <c r="C10" s="6">
         <v>10</v>
@@ -9217,7 +9241,7 @@
         <v>398</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>442</v>
+        <v>711</v>
       </c>
       <c r="C11" s="6">
         <v>5</v>
@@ -9240,7 +9264,7 @@
         <v>399</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>243</v>
+        <v>712</v>
       </c>
       <c r="C12" s="6">
         <v>40</v>
@@ -9263,7 +9287,7 @@
         <v>400</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>243</v>
+        <v>712</v>
       </c>
       <c r="C13" s="6">
         <v>25</v>
@@ -9286,7 +9310,7 @@
         <v>401</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>243</v>
+        <v>712</v>
       </c>
       <c r="C14" s="6">
         <v>15</v>
@@ -9309,7 +9333,7 @@
         <v>402</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>243</v>
+        <v>712</v>
       </c>
       <c r="C15" s="6">
         <v>10</v>
@@ -9332,7 +9356,7 @@
         <v>403</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>243</v>
+        <v>712</v>
       </c>
       <c r="C16" s="6">
         <v>10</v>
@@ -9355,7 +9379,7 @@
         <v>404</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>244</v>
+        <v>713</v>
       </c>
       <c r="C17" s="6">
         <v>35</v>
@@ -9378,7 +9402,7 @@
         <v>433</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>244</v>
+        <v>713</v>
       </c>
       <c r="C18" s="6">
         <v>25</v>
@@ -9401,7 +9425,7 @@
         <v>434</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>244</v>
+        <v>713</v>
       </c>
       <c r="C19" s="6">
         <v>20</v>
@@ -9424,7 +9448,7 @@
         <v>435</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>244</v>
+        <v>713</v>
       </c>
       <c r="C20" s="6">
         <v>10</v>
@@ -9447,7 +9471,7 @@
         <v>436</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>244</v>
+        <v>713</v>
       </c>
       <c r="C21" s="6">
         <v>10</v>
@@ -9470,7 +9494,7 @@
         <v>437</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>245</v>
+        <v>714</v>
       </c>
       <c r="C22" s="6">
         <v>35</v>
@@ -9493,7 +9517,7 @@
         <v>438</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>245</v>
+        <v>714</v>
       </c>
       <c r="C23" s="6">
         <v>25</v>
@@ -9516,7 +9540,7 @@
         <v>439</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>245</v>
+        <v>714</v>
       </c>
       <c r="C24" s="6">
         <v>15</v>
@@ -9539,7 +9563,7 @@
         <v>440</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>245</v>
+        <v>714</v>
       </c>
       <c r="C25" s="6">
         <v>15</v>
@@ -9562,7 +9586,7 @@
         <v>443</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>245</v>
+        <v>714</v>
       </c>
       <c r="C26" s="6">
         <v>10</v>
@@ -9585,7 +9609,7 @@
         <v>444</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>246</v>
+        <v>715</v>
       </c>
       <c r="C27" s="6">
         <v>35</v>
@@ -9608,7 +9632,7 @@
         <v>445</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>246</v>
+        <v>715</v>
       </c>
       <c r="C28" s="6">
         <v>25</v>
@@ -9631,7 +9655,7 @@
         <v>446</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>246</v>
+        <v>715</v>
       </c>
       <c r="C29" s="6">
         <v>15</v>
@@ -9654,7 +9678,7 @@
         <v>447</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>246</v>
+        <v>715</v>
       </c>
       <c r="C30" s="6">
         <v>15</v>
@@ -9677,7 +9701,7 @@
         <v>448</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>246</v>
+        <v>715</v>
       </c>
       <c r="C31" s="6">
         <v>10</v>
@@ -9700,7 +9724,7 @@
         <v>449</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>247</v>
+        <v>716</v>
       </c>
       <c r="C32" s="6">
         <v>40</v>
@@ -9723,7 +9747,7 @@
         <v>450</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>247</v>
+        <v>716</v>
       </c>
       <c r="C33" s="6">
         <v>25</v>
@@ -9746,7 +9770,7 @@
         <v>451</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>247</v>
+        <v>716</v>
       </c>
       <c r="C34" s="6">
         <v>15</v>
@@ -9769,7 +9793,7 @@
         <v>452</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>247</v>
+        <v>716</v>
       </c>
       <c r="C35" s="6">
         <v>10</v>
@@ -9792,7 +9816,7 @@
         <v>453</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>247</v>
+        <v>716</v>
       </c>
       <c r="C36" s="6">
         <v>10</v>
@@ -9815,7 +9839,7 @@
         <v>454</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>248</v>
+        <v>717</v>
       </c>
       <c r="C37" s="6">
         <v>35</v>
@@ -9838,7 +9862,7 @@
         <v>455</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>248</v>
+        <v>717</v>
       </c>
       <c r="C38" s="6">
         <v>25</v>
@@ -9861,7 +9885,7 @@
         <v>456</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>248</v>
+        <v>717</v>
       </c>
       <c r="C39" s="6">
         <v>20</v>
@@ -9884,7 +9908,7 @@
         <v>457</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>248</v>
+        <v>717</v>
       </c>
       <c r="C40" s="6">
         <v>10</v>
@@ -9907,7 +9931,7 @@
         <v>458</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>248</v>
+        <v>717</v>
       </c>
       <c r="C41" s="6">
         <v>10</v>
